--- a/raw-xlsx/82Chapra_2026_Form20.xlsx
+++ b/raw-xlsx/82Chapra_2026_Form20.xlsx
@@ -460,7 +460,7 @@
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.17890520694259</v>
+        <v>0.1789052069425901</v>
       </c>
       <c r="D2" s="4" t="n">
         <v>134</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.397863818424566</v>
+        <v>0.3978638184245661</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>298</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.393858477970627</v>
+        <v>0.3938584779706275</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>295</v>
@@ -597,25 +597,25 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.368843069873998</v>
+        <v>0.3688430698739977</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>322</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.00916380297823597</v>
+        <v>0.009163802978235968</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>8</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.5429553264604809</v>
+        <v>0.5429553264604811</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>474</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.0103092783505155</v>
+        <v>0.01030927835051546</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>9</v>
@@ -648,19 +648,19 @@
         <v>191</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.331058020477816</v>
+        <v>0.3310580204778157</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>291</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.425483503981797</v>
+        <v>0.4254835039817975</v>
       </c>
       <c r="H4" s="4" t="n">
         <v>374</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.00341296928327645</v>
+        <v>0.003412969283276451</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>3</v>
@@ -687,25 +687,25 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.317660550458716</v>
+        <v>0.3176605504587156</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>277</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.0217889908256881</v>
+        <v>0.02178899082568807</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>19</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.610091743119266</v>
+        <v>0.6100917431192661</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>532</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.0091743119266055</v>
+        <v>0.009174311926605505</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>8</v>
@@ -732,13 +732,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.157490396927017</v>
+        <v>0.1574903969270166</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>123</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.539052496798976</v>
+        <v>0.5390524967989757</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>421</v>
@@ -750,7 +750,7 @@
         <v>207</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.00640204865556978</v>
+        <v>0.006402048655569782</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>5</v>
@@ -777,13 +777,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.241581259150805</v>
+        <v>0.2415812591508053</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>165</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.295754026354319</v>
+        <v>0.2957540263543192</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>202</v>
@@ -795,7 +795,7 @@
         <v>290</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.008784773060029279</v>
+        <v>0.008784773060029283</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>6</v>
@@ -828,19 +828,19 @@
         <v>460</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0.0107615894039735</v>
+        <v>0.01076158940397351</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>13</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.576158940397351</v>
+        <v>0.5761589403973509</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>696</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.008278145695364241</v>
+        <v>0.008278145695364239</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>10</v>
@@ -867,25 +867,25 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.378861788617886</v>
+        <v>0.3788617886178862</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>233</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.0536585365853659</v>
+        <v>0.05365853658536585</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>33</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.546341463414634</v>
+        <v>0.5463414634146342</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>336</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.00487804878048781</v>
+        <v>0.004878048780487805</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>3</v>
@@ -912,25 +912,25 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.464634146341463</v>
+        <v>0.4646341463414634</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>381</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.0548780487804878</v>
+        <v>0.05487804878048781</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>45</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.440243902439024</v>
+        <v>0.4402439024390244</v>
       </c>
       <c r="H10" s="4" t="n">
         <v>361</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.0121951219512195</v>
+        <v>0.01219512195121951</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>10</v>
@@ -957,25 +957,25 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.341163310961969</v>
+        <v>0.3411633109619687</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>305</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0.0682326621923937</v>
+        <v>0.06823266219239374</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>61</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.550335570469799</v>
+        <v>0.5503355704697986</v>
       </c>
       <c r="H11" s="4" t="n">
         <v>492</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.00559284116331096</v>
+        <v>0.005592841163310962</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>5</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.353500432152118</v>
+        <v>0.3535004321521176</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>409</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.010371650821089</v>
+        <v>0.01037165082108902</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>12</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.607605877268799</v>
+        <v>0.6076058772687987</v>
       </c>
       <c r="H12" s="4" t="n">
         <v>703</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.00691443388072602</v>
+        <v>0.006914433880726016</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>8</v>
@@ -1047,25 +1047,25 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.465634075508228</v>
+        <v>0.4656340755082284</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>481</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.00774443368828654</v>
+        <v>0.007744433688286544</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>8</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.487899322362052</v>
+        <v>0.4878993223620523</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>504</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.008712487899322359</v>
+        <v>0.008712487899322363</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>9</v>
@@ -1104,13 +1104,13 @@
         <v>15</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.515837104072398</v>
+        <v>0.5158371040723982</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>456</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.007918552036199089</v>
+        <v>0.007918552036199095</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>7</v>
@@ -1143,19 +1143,19 @@
         <v>165</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.0101596516690856</v>
+        <v>0.01015965166908563</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>7</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.705370101596517</v>
+        <v>0.7053701015965167</v>
       </c>
       <c r="H15" s="4" t="n">
         <v>486</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.0101596516690856</v>
+        <v>0.01015965166908563</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>7</v>
@@ -1182,25 +1182,25 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.0123626373626374</v>
+        <v>0.01236263736263736</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>9</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.837912087912088</v>
+        <v>0.8379120879120879</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>610</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.115384615384615</v>
+        <v>0.1153846153846154</v>
       </c>
       <c r="H16" s="4" t="n">
         <v>84</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.00824175824175824</v>
+        <v>0.008241758241758242</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>6</v>
@@ -1227,25 +1227,25 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.0337601862630966</v>
+        <v>0.03376018626309663</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>29</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.745052386495926</v>
+        <v>0.7450523864959255</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>640</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.20139697322468</v>
+        <v>0.2013969732246799</v>
       </c>
       <c r="H17" s="4" t="n">
         <v>173</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.00582072176949942</v>
+        <v>0.005820721769499418</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>5</v>
@@ -1272,19 +1272,19 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.00735294117647059</v>
+        <v>0.007352941176470588</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0.563725490196078</v>
+        <v>0.5637254901960784</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>230</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.419117647058823</v>
+        <v>0.4191176470588235</v>
       </c>
       <c r="H18" s="4" t="n">
         <v>171</v>
@@ -1317,25 +1317,25 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.008350730688935279</v>
+        <v>0.008350730688935281</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>8</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0.701461377870564</v>
+        <v>0.7014613778705637</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>672</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.260960334029228</v>
+        <v>0.2609603340292276</v>
       </c>
       <c r="H19" s="4" t="n">
         <v>250</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.008350730688935279</v>
+        <v>0.008350730688935281</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>8</v>
@@ -1362,25 +1362,25 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.207582938388626</v>
+        <v>0.2075829383886256</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>219</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.0123222748815166</v>
+        <v>0.01232227488151659</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>13</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.750710900473934</v>
+        <v>0.7507109004739336</v>
       </c>
       <c r="H20" s="4" t="n">
         <v>792</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.004739336492891</v>
+        <v>0.004739336492890996</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>5</v>
@@ -1407,25 +1407,25 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0.156462585034014</v>
+        <v>0.1564625850340136</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>115</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.266666666666667</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>196</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.552380952380952</v>
+        <v>0.5523809523809524</v>
       </c>
       <c r="H21" s="4" t="n">
         <v>406</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.00408163265306122</v>
+        <v>0.004081632653061225</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>3</v>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.106325706594886</v>
+        <v>0.1063257065948856</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>79</v>
@@ -1464,13 +1464,13 @@
         <v>120</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.694481830417227</v>
+        <v>0.6944818304172274</v>
       </c>
       <c r="H22" s="4" t="n">
         <v>516</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.00672947510094213</v>
+        <v>0.006729475100942127</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>5</v>
@@ -1497,13 +1497,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.0472727272727273</v>
+        <v>0.04727272727272727</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>26</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.443636363636364</v>
+        <v>0.4436363636363637</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>244</v>
@@ -1515,7 +1515,7 @@
         <v>253</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.00727272727272727</v>
+        <v>0.007272727272727273</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>4</v>
@@ -1542,25 +1542,25 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.0919732441471572</v>
+        <v>0.09197324414715718</v>
       </c>
       <c r="D24" s="4" t="n">
         <v>55</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0.190635451505017</v>
+        <v>0.1906354515050167</v>
       </c>
       <c r="F24" s="4" t="n">
         <v>114</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.683946488294314</v>
+        <v>0.6839464882943144</v>
       </c>
       <c r="H24" s="4" t="n">
         <v>409</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.00836120401337793</v>
+        <v>0.008361204013377926</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>5</v>
@@ -1587,25 +1587,25 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0.00927152317880795</v>
+        <v>0.009271523178807948</v>
       </c>
       <c r="D25" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.843708609271523</v>
+        <v>0.8437086092715231</v>
       </c>
       <c r="F25" s="4" t="n">
         <v>637</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.124503311258278</v>
+        <v>0.1245033112582781</v>
       </c>
       <c r="H25" s="4" t="n">
         <v>94</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.00397350993377483</v>
+        <v>0.003973509933774834</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>3</v>
@@ -1632,25 +1632,25 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.186991869918699</v>
+        <v>0.1869918699186992</v>
       </c>
       <c r="D26" s="4" t="n">
         <v>92</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>0.215447154471545</v>
+        <v>0.2154471544715447</v>
       </c>
       <c r="F26" s="4" t="n">
         <v>106</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.5772357723577241</v>
+        <v>0.5772357723577236</v>
       </c>
       <c r="H26" s="4" t="n">
         <v>284</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.00203252032520325</v>
+        <v>0.002032520325203252</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>1</v>
@@ -1677,25 +1677,25 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.295774647887324</v>
+        <v>0.2957746478873239</v>
       </c>
       <c r="D27" s="4" t="n">
         <v>273</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.0715059588299025</v>
+        <v>0.07150595882990249</v>
       </c>
       <c r="F27" s="4" t="n">
         <v>66</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.579631635969664</v>
+        <v>0.5796316359696642</v>
       </c>
       <c r="H27" s="4" t="n">
         <v>535</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.0140845070422535</v>
+        <v>0.01408450704225352</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>13</v>
@@ -1722,25 +1722,25 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.383886255924171</v>
+        <v>0.3838862559241706</v>
       </c>
       <c r="D28" s="4" t="n">
         <v>324</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.008293838862559241</v>
+        <v>0.008293838862559242</v>
       </c>
       <c r="F28" s="4" t="n">
         <v>7</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.575829383886256</v>
+        <v>0.5758293838862559</v>
       </c>
       <c r="H28" s="4" t="n">
         <v>486</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.0023696682464455</v>
+        <v>0.002369668246445498</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>2</v>
@@ -1767,13 +1767,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.559096945551129</v>
+        <v>0.5590969455511288</v>
       </c>
       <c r="D29" s="4" t="n">
         <v>421</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.00664010624169987</v>
+        <v>0.006640106241699867</v>
       </c>
       <c r="F29" s="4" t="n">
         <v>5</v>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.260249554367201</v>
+        <v>0.2602495543672014</v>
       </c>
       <c r="D30" s="4" t="n">
         <v>146</v>
@@ -1824,7 +1824,7 @@
         <v>10</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.693404634581105</v>
+        <v>0.6934046345811051</v>
       </c>
       <c r="H30" s="4" t="n">
         <v>389</v>
@@ -1857,25 +1857,25 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.250954198473282</v>
+        <v>0.2509541984732824</v>
       </c>
       <c r="D31" s="4" t="n">
         <v>263</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0.0295801526717557</v>
+        <v>0.02958015267175573</v>
       </c>
       <c r="F31" s="4" t="n">
         <v>31</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.678435114503817</v>
+        <v>0.6784351145038168</v>
       </c>
       <c r="H31" s="4" t="n">
         <v>711</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.0066793893129771</v>
+        <v>0.006679389312977099</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>7</v>
@@ -1902,25 +1902,25 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>0.293302540415704</v>
+        <v>0.2933025404157044</v>
       </c>
       <c r="D32" s="4" t="n">
         <v>254</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>0.0069284064665127</v>
+        <v>0.006928406466512702</v>
       </c>
       <c r="F32" s="4" t="n">
         <v>6</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.662817551963048</v>
+        <v>0.6628175519630485</v>
       </c>
       <c r="H32" s="4" t="n">
         <v>574</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.00577367205542725</v>
+        <v>0.005773672055427252</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>5</v>
@@ -1947,7 +1947,7 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>0.507936507936508</v>
+        <v>0.5079365079365079</v>
       </c>
       <c r="D33" s="4" t="n">
         <v>352</v>
@@ -1959,13 +1959,13 @@
         <v>7</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.453102453102453</v>
+        <v>0.4531024531024531</v>
       </c>
       <c r="H33" s="4" t="n">
         <v>314</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.00288600288600289</v>
+        <v>0.002886002886002886</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>2</v>
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.396526772793053</v>
+        <v>0.3965267727930535</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>274</v>
@@ -2004,13 +2004,13 @@
         <v>5</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.571635311143271</v>
+        <v>0.5716353111432706</v>
       </c>
       <c r="H34" s="4" t="n">
         <v>395</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.00289435600578871</v>
+        <v>0.002894356005788712</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>2</v>
@@ -2037,25 +2037,25 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0.220472440944882</v>
+        <v>0.2204724409448819</v>
       </c>
       <c r="D35" s="4" t="n">
         <v>140</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>0.0062992125984252</v>
+        <v>0.006299212598425197</v>
       </c>
       <c r="F35" s="4" t="n">
         <v>4</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.740157480314961</v>
+        <v>0.7401574803149606</v>
       </c>
       <c r="H35" s="4" t="n">
         <v>470</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0.0031496062992126</v>
+        <v>0.003149606299212598</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>2</v>
@@ -2082,25 +2082,25 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.347763347763348</v>
+        <v>0.3477633477633478</v>
       </c>
       <c r="D36" s="4" t="n">
         <v>241</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.07792207792207791</v>
+        <v>0.07792207792207792</v>
       </c>
       <c r="F36" s="4" t="n">
         <v>54</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.5440115440115439</v>
+        <v>0.5440115440115441</v>
       </c>
       <c r="H36" s="4" t="n">
         <v>377</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.00577200577200577</v>
+        <v>0.005772005772005772</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>4</v>
@@ -2172,19 +2172,19 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>0.5349264705882349</v>
+        <v>0.5349264705882353</v>
       </c>
       <c r="D38" s="4" t="n">
         <v>291</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>0.0386029411764706</v>
+        <v>0.03860294117647059</v>
       </c>
       <c r="F38" s="4" t="n">
         <v>21</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.408088235294118</v>
+        <v>0.4080882352941176</v>
       </c>
       <c r="H38" s="4" t="n">
         <v>222</v>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0.56578947368421</v>
+        <v>0.5657894736842105</v>
       </c>
       <c r="D39" s="4" t="n">
         <v>301</v>
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.392857142857143</v>
+        <v>0.3928571428571428</v>
       </c>
       <c r="H39" s="4" t="n">
         <v>209</v>
@@ -2262,25 +2262,25 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0.291891891891892</v>
+        <v>0.2918918918918919</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>162</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0.216216216216216</v>
+        <v>0.2162162162162162</v>
       </c>
       <c r="F40" s="4" t="n">
         <v>120</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.463063063063063</v>
+        <v>0.4630630630630631</v>
       </c>
       <c r="H40" s="4" t="n">
         <v>257</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.009009009009009011</v>
+        <v>0.009009009009009009</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>5</v>
@@ -2319,13 +2319,13 @@
         <v>4</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.553784860557769</v>
+        <v>0.5537848605577689</v>
       </c>
       <c r="H41" s="4" t="n">
         <v>278</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.0139442231075697</v>
+        <v>0.01394422310756972</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>7</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>0.0108342361863489</v>
+        <v>0.01083423618634886</v>
       </c>
       <c r="D42" s="4" t="n">
         <v>10</v>
@@ -2364,13 +2364,13 @@
         <v>800</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.107258938244854</v>
+        <v>0.1072589382448537</v>
       </c>
       <c r="H42" s="4" t="n">
         <v>99</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.00325027085590466</v>
+        <v>0.003250270855904659</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>3</v>
@@ -2397,25 +2397,25 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0.313837375178317</v>
+        <v>0.3138373751783167</v>
       </c>
       <c r="D43" s="4" t="n">
         <v>220</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0.0556348074179743</v>
+        <v>0.05563480741797432</v>
       </c>
       <c r="F43" s="4" t="n">
         <v>39</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.583452211126961</v>
+        <v>0.5834522111269614</v>
       </c>
       <c r="H43" s="4" t="n">
         <v>409</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.014265335235378</v>
+        <v>0.01426533523537803</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>10</v>
@@ -2442,25 +2442,25 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.0981210855949896</v>
+        <v>0.09812108559498957</v>
       </c>
       <c r="D44" s="4" t="n">
         <v>47</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>0.5219206680584551</v>
+        <v>0.5219206680584552</v>
       </c>
       <c r="F44" s="4" t="n">
         <v>250</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.363256784968685</v>
+        <v>0.3632567849686847</v>
       </c>
       <c r="H44" s="4" t="n">
         <v>174</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.00626304801670146</v>
+        <v>0.006263048016701462</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>3</v>
@@ -2487,25 +2487,25 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>0.199186991869919</v>
+        <v>0.1991869918699187</v>
       </c>
       <c r="D45" s="4" t="n">
         <v>98</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>0.40650406504065</v>
+        <v>0.4065040650406504</v>
       </c>
       <c r="F45" s="4" t="n">
         <v>200</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.34349593495935</v>
+        <v>0.3434959349593496</v>
       </c>
       <c r="H45" s="4" t="n">
         <v>169</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.0203252032520325</v>
+        <v>0.02032520325203252</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>10</v>
@@ -2538,19 +2538,19 @@
         <v>101</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0.184757505773672</v>
+        <v>0.1847575057736721</v>
       </c>
       <c r="F46" s="4" t="n">
         <v>80</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.565819861431871</v>
+        <v>0.5658198614318707</v>
       </c>
       <c r="H46" s="4" t="n">
         <v>245</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.0069284064665127</v>
+        <v>0.006928406466512702</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>3</v>
@@ -2577,25 +2577,25 @@
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>0.34392523364486</v>
+        <v>0.3439252336448598</v>
       </c>
       <c r="D47" s="4" t="n">
         <v>184</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0.0373831775700935</v>
+        <v>0.03738317757009346</v>
       </c>
       <c r="F47" s="4" t="n">
         <v>20</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.5981308411214949</v>
+        <v>0.5981308411214953</v>
       </c>
       <c r="H47" s="4" t="n">
         <v>320</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.00186915887850467</v>
+        <v>0.001869158878504673</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>1</v>
@@ -2622,19 +2622,19 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.25920471281296</v>
+        <v>0.2592047128129603</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>176</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.306332842415317</v>
+        <v>0.3063328424153167</v>
       </c>
       <c r="F48" s="4" t="n">
         <v>208</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.424153166421208</v>
+        <v>0.4241531664212077</v>
       </c>
       <c r="H48" s="4" t="n">
         <v>288</v>
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>0.166892808683853</v>
+        <v>0.1668928086838534</v>
       </c>
       <c r="D49" s="4" t="n">
         <v>123</v>
@@ -2679,7 +2679,7 @@
         <v>304</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.390773405698779</v>
+        <v>0.3907734056987788</v>
       </c>
       <c r="H49" s="4" t="n">
         <v>288</v>
@@ -2718,7 +2718,7 @@
         <v>310</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>0.0134638922888617</v>
+        <v>0.01346389228886169</v>
       </c>
       <c r="F50" s="4" t="n">
         <v>11</v>
@@ -2730,7 +2730,7 @@
         <v>462</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.00367197062423501</v>
+        <v>0.003671970624235006</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>3</v>
@@ -2757,25 +2757,25 @@
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>0.329138431752178</v>
+        <v>0.3291384317521781</v>
       </c>
       <c r="D51" s="4" t="n">
         <v>340</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>0.0890609874152952</v>
+        <v>0.08906098741529525</v>
       </c>
       <c r="F51" s="4" t="n">
         <v>92</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.545014520813166</v>
+        <v>0.5450145208131656</v>
       </c>
       <c r="H51" s="4" t="n">
         <v>563</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.00387221684414327</v>
+        <v>0.003872216844143272</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>4</v>
@@ -2802,19 +2802,19 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>0.236593059936908</v>
+        <v>0.2365930599369085</v>
       </c>
       <c r="D52" s="4" t="n">
         <v>150</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>0.082018927444795</v>
+        <v>0.08201892744479496</v>
       </c>
       <c r="F52" s="4" t="n">
         <v>52</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.649842271293375</v>
+        <v>0.6498422712933754</v>
       </c>
       <c r="H52" s="4" t="n">
         <v>412</v>
@@ -2847,19 +2847,19 @@
         </is>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0.191256830601093</v>
+        <v>0.1912568306010929</v>
       </c>
       <c r="D53" s="4" t="n">
         <v>105</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0.0182149362477231</v>
+        <v>0.01821493624772313</v>
       </c>
       <c r="F53" s="4" t="n">
         <v>10</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.7285974499089251</v>
+        <v>0.7285974499089253</v>
       </c>
       <c r="H53" s="4" t="n">
         <v>400</v>
@@ -2898,19 +2898,19 @@
         <v>370</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>0.035799522673031</v>
+        <v>0.03579952267303103</v>
       </c>
       <c r="F54" s="4" t="n">
         <v>30</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.478520286396181</v>
+        <v>0.4785202863961814</v>
       </c>
       <c r="H54" s="4" t="n">
         <v>401</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.0035799522673031</v>
+        <v>0.003579952267303103</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>3</v>
@@ -2937,25 +2937,25 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>0.385321100917431</v>
+        <v>0.3853211009174312</v>
       </c>
       <c r="D55" s="4" t="n">
         <v>210</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>0.0403669724770642</v>
+        <v>0.04036697247706422</v>
       </c>
       <c r="F55" s="4" t="n">
         <v>22</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.526605504587156</v>
+        <v>0.5266055045871559</v>
       </c>
       <c r="H55" s="4" t="n">
         <v>287</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.0055045871559633</v>
+        <v>0.005504587155963303</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>3</v>
@@ -2982,13 +2982,13 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0.143051771117166</v>
+        <v>0.1430517711171662</v>
       </c>
       <c r="D56" s="4" t="n">
         <v>105</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0.346049046321526</v>
+        <v>0.3460490463215259</v>
       </c>
       <c r="F56" s="4" t="n">
         <v>254</v>
@@ -3000,7 +3000,7 @@
         <v>363</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.00136239782016349</v>
+        <v>0.001362397820163488</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>1</v>
@@ -3033,13 +3033,13 @@
         <v>192</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0.0851851851851852</v>
+        <v>0.08518518518518518</v>
       </c>
       <c r="F57" s="4" t="n">
         <v>69</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.650617283950617</v>
+        <v>0.6506172839506172</v>
       </c>
       <c r="H57" s="4" t="n">
         <v>527</v>
@@ -3072,19 +3072,19 @@
         </is>
       </c>
       <c r="C58" s="3" t="n">
-        <v>0.190677966101695</v>
+        <v>0.1906779661016949</v>
       </c>
       <c r="D58" s="4" t="n">
         <v>180</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>0.582627118644068</v>
+        <v>0.5826271186440678</v>
       </c>
       <c r="F58" s="4" t="n">
         <v>550</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.212923728813559</v>
+        <v>0.2129237288135593</v>
       </c>
       <c r="H58" s="4" t="n">
         <v>201</v>
@@ -3117,13 +3117,13 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>0.419154228855721</v>
+        <v>0.4191542288557214</v>
       </c>
       <c r="D59" s="4" t="n">
         <v>337</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>0.166666666666667</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="F59" s="4" t="n">
         <v>134</v>
@@ -3135,7 +3135,7 @@
         <v>314</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.0124378109452736</v>
+        <v>0.01243781094527363</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>10</v>
@@ -3162,25 +3162,25 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>0.443037974683544</v>
+        <v>0.4430379746835443</v>
       </c>
       <c r="D60" s="4" t="n">
         <v>280</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>0.0126582278481013</v>
+        <v>0.01265822784810127</v>
       </c>
       <c r="F60" s="4" t="n">
         <v>8</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.490506329113924</v>
+        <v>0.4905063291139241</v>
       </c>
       <c r="H60" s="4" t="n">
         <v>310</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.0126582278481013</v>
+        <v>0.01265822784810127</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>8</v>
@@ -3207,7 +3207,7 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>0.340425531914894</v>
+        <v>0.3404255319148936</v>
       </c>
       <c r="D61" s="4" t="n">
         <v>192</v>
@@ -3219,7 +3219,7 @@
         <v>7</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.627659574468085</v>
+        <v>0.6276595744680851</v>
       </c>
       <c r="H61" s="4" t="n">
         <v>354</v>
@@ -3252,25 +3252,25 @@
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>0.570469798657718</v>
+        <v>0.5704697986577181</v>
       </c>
       <c r="D62" s="4" t="n">
         <v>340</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>0.00167785234899329</v>
+        <v>0.001677852348993289</v>
       </c>
       <c r="F62" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.414429530201342</v>
+        <v>0.4144295302013423</v>
       </c>
       <c r="H62" s="4" t="n">
         <v>247</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.00671140939597315</v>
+        <v>0.006711409395973154</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>4</v>
@@ -3297,13 +3297,13 @@
         </is>
       </c>
       <c r="C63" s="3" t="n">
-        <v>0.364583333333333</v>
+        <v>0.3645833333333333</v>
       </c>
       <c r="D63" s="4" t="n">
         <v>210</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>0.0399305555555556</v>
+        <v>0.03993055555555555</v>
       </c>
       <c r="F63" s="4" t="n">
         <v>23</v>
@@ -3315,7 +3315,7 @@
         <v>324</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0.0121527777777778</v>
+        <v>0.01215277777777778</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>7</v>
@@ -3342,25 +3342,25 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0.268364348677767</v>
+        <v>0.2683643486777669</v>
       </c>
       <c r="D64" s="4" t="n">
         <v>274</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0.0107737512242899</v>
+        <v>0.01077375122428991</v>
       </c>
       <c r="F64" s="4" t="n">
         <v>11</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.698334965719883</v>
+        <v>0.6983349657198825</v>
       </c>
       <c r="H64" s="4" t="n">
         <v>713</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.00489715964740451</v>
+        <v>0.004897159647404506</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>5</v>
@@ -3387,25 +3387,25 @@
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>0.254777070063694</v>
+        <v>0.2547770700636943</v>
       </c>
       <c r="D65" s="4" t="n">
         <v>80</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>0.009554140127388529</v>
+        <v>0.009554140127388535</v>
       </c>
       <c r="F65" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.700636942675159</v>
+        <v>0.7006369426751592</v>
       </c>
       <c r="H65" s="4" t="n">
         <v>220</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0.009554140127388529</v>
+        <v>0.009554140127388535</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>3</v>
@@ -3432,25 +3432,25 @@
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>0.186086956521739</v>
+        <v>0.1860869565217391</v>
       </c>
       <c r="D66" s="4" t="n">
         <v>107</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>0.00173913043478261</v>
+        <v>0.001739130434782609</v>
       </c>
       <c r="F66" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.796521739130435</v>
+        <v>0.7965217391304348</v>
       </c>
       <c r="H66" s="4" t="n">
         <v>458</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.00347826086956522</v>
+        <v>0.003478260869565218</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>2</v>
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0.154731457800512</v>
+        <v>0.1547314578005115</v>
       </c>
       <c r="D67" s="4" t="n">
         <v>121</v>
@@ -3489,13 +3489,13 @@
         <v>5</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.81074168797954</v>
+        <v>0.8107416879795396</v>
       </c>
       <c r="H67" s="4" t="n">
         <v>634</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0.0166240409207161</v>
+        <v>0.01662404092071611</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>13</v>
@@ -3522,25 +3522,25 @@
         </is>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.135593220338983</v>
+        <v>0.1355932203389831</v>
       </c>
       <c r="D68" s="4" t="n">
         <v>80</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.00169491525423729</v>
+        <v>0.001694915254237288</v>
       </c>
       <c r="F68" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.845762711864407</v>
+        <v>0.8457627118644068</v>
       </c>
       <c r="H68" s="4" t="n">
         <v>499</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.011864406779661</v>
+        <v>0.01186440677966102</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>7</v>
@@ -3567,13 +3567,13 @@
         </is>
       </c>
       <c r="C69" s="3" t="n">
-        <v>0.0928270042194093</v>
+        <v>0.09282700421940929</v>
       </c>
       <c r="D69" s="4" t="n">
         <v>110</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>0.0236286919831224</v>
+        <v>0.02362869198312236</v>
       </c>
       <c r="F69" s="4" t="n">
         <v>28</v>
@@ -3612,7 +3612,7 @@
         </is>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0.176020408163265</v>
+        <v>0.1760204081632653</v>
       </c>
       <c r="D70" s="4" t="n">
         <v>69</v>
@@ -3624,13 +3624,13 @@
         <v>0</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.788265306122449</v>
+        <v>0.7882653061224489</v>
       </c>
       <c r="H70" s="4" t="n">
         <v>309</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.0229591836734694</v>
+        <v>0.02295918367346939</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>9</v>
@@ -3663,19 +3663,19 @@
         <v>184</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0.0129107981220657</v>
+        <v>0.01291079812206573</v>
       </c>
       <c r="F71" s="4" t="n">
         <v>11</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.727699530516432</v>
+        <v>0.7276995305164319</v>
       </c>
       <c r="H71" s="4" t="n">
         <v>620</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.0164319248826291</v>
+        <v>0.01643192488262911</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>14</v>
@@ -3702,25 +3702,25 @@
         </is>
       </c>
       <c r="C72" s="3" t="n">
-        <v>0.269360269360269</v>
+        <v>0.2693602693602694</v>
       </c>
       <c r="D72" s="4" t="n">
         <v>160</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>0.0488215488215488</v>
+        <v>0.04882154882154882</v>
       </c>
       <c r="F72" s="4" t="n">
         <v>29</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.641414141414141</v>
+        <v>0.6414141414141414</v>
       </c>
       <c r="H72" s="4" t="n">
         <v>381</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.0168350168350168</v>
+        <v>0.01683501683501683</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>10</v>
@@ -3747,25 +3747,25 @@
         </is>
       </c>
       <c r="C73" s="3" t="n">
-        <v>0.362030905077263</v>
+        <v>0.3620309050772627</v>
       </c>
       <c r="D73" s="4" t="n">
         <v>328</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>0.0165562913907285</v>
+        <v>0.01655629139072848</v>
       </c>
       <c r="F73" s="4" t="n">
         <v>15</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.5121412803532009</v>
+        <v>0.5121412803532008</v>
       </c>
       <c r="H73" s="4" t="n">
         <v>464</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.0894039735099338</v>
+        <v>0.08940397350993377</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>81</v>
@@ -3792,25 +3792,25 @@
         </is>
       </c>
       <c r="C74" s="3" t="n">
-        <v>0.425925925925926</v>
+        <v>0.4259259259259259</v>
       </c>
       <c r="D74" s="4" t="n">
         <v>322</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>0.0211640211640212</v>
+        <v>0.02116402116402116</v>
       </c>
       <c r="F74" s="4" t="n">
         <v>16</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.514550264550265</v>
+        <v>0.5145502645502645</v>
       </c>
       <c r="H74" s="4" t="n">
         <v>389</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0.0238095238095238</v>
+        <v>0.02380952380952381</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>18</v>
@@ -3837,25 +3837,25 @@
         </is>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.138849929873773</v>
+        <v>0.1388499298737728</v>
       </c>
       <c r="D75" s="4" t="n">
         <v>99</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.5483870967741939</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="F75" s="4" t="n">
         <v>391</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.284712482468443</v>
+        <v>0.2847124824684432</v>
       </c>
       <c r="H75" s="4" t="n">
         <v>203</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.00561009817671809</v>
+        <v>0.005610098176718092</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>4</v>
@@ -3882,25 +3882,25 @@
         </is>
       </c>
       <c r="C76" s="3" t="n">
-        <v>0.333762886597938</v>
+        <v>0.3337628865979381</v>
       </c>
       <c r="D76" s="4" t="n">
         <v>259</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>0.0167525773195876</v>
+        <v>0.01675257731958763</v>
       </c>
       <c r="F76" s="4" t="n">
         <v>13</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.622422680412371</v>
+        <v>0.6224226804123711</v>
       </c>
       <c r="H76" s="4" t="n">
         <v>483</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.00128865979381443</v>
+        <v>0.001288659793814433</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>1</v>
@@ -3927,7 +3927,7 @@
         </is>
       </c>
       <c r="C77" s="3" t="n">
-        <v>0.44672131147541</v>
+        <v>0.4467213114754098</v>
       </c>
       <c r="D77" s="4" t="n">
         <v>327</v>
@@ -3939,7 +3939,7 @@
         <v>4</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.528688524590164</v>
+        <v>0.5286885245901639</v>
       </c>
       <c r="H77" s="4" t="n">
         <v>387</v>
@@ -3972,25 +3972,25 @@
         </is>
       </c>
       <c r="C78" s="3" t="n">
-        <v>0.114657210401891</v>
+        <v>0.1146572104018913</v>
       </c>
       <c r="D78" s="4" t="n">
         <v>97</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>0.0177304964539007</v>
+        <v>0.01773049645390071</v>
       </c>
       <c r="F78" s="4" t="n">
         <v>15</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.8274231678487</v>
+        <v>0.8274231678486997</v>
       </c>
       <c r="H78" s="4" t="n">
         <v>700</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.0130023640661939</v>
+        <v>0.01300236406619385</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>11</v>
@@ -4017,19 +4017,19 @@
         </is>
       </c>
       <c r="C79" s="3" t="n">
-        <v>0.0769230769230769</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="D79" s="4" t="n">
         <v>40</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>0.00384615384615385</v>
+        <v>0.003846153846153846</v>
       </c>
       <c r="F79" s="4" t="n">
         <v>2</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.905769230769231</v>
+        <v>0.9057692307692308</v>
       </c>
       <c r="H79" s="4" t="n">
         <v>471</v>
@@ -4068,13 +4068,13 @@
         <v>0</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.614213197969543</v>
+        <v>0.6142131979695431</v>
       </c>
       <c r="F80" s="4" t="n">
         <v>363</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.357021996615905</v>
+        <v>0.3570219966159052</v>
       </c>
       <c r="H80" s="4" t="n">
         <v>211</v>
@@ -4113,13 +4113,13 @@
         <v>21</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>0.166666666666667</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="F81" s="4" t="n">
         <v>112</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.7886904761904761</v>
+        <v>0.7886904761904762</v>
       </c>
       <c r="H81" s="4" t="n">
         <v>530</v>
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="C82" s="3" t="n">
-        <v>0.00441176470588235</v>
+        <v>0.004411764705882353</v>
       </c>
       <c r="D82" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>0.911764705882353</v>
+        <v>0.9117647058823529</v>
       </c>
       <c r="F82" s="4" t="n">
         <v>620</v>
@@ -4170,7 +4170,7 @@
         <v>45</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.00147058823529412</v>
+        <v>0.001470588235294118</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>1</v>
@@ -4197,25 +4197,25 @@
         </is>
       </c>
       <c r="C83" s="3" t="n">
-        <v>0.007990867579908681</v>
+        <v>0.007990867579908675</v>
       </c>
       <c r="D83" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>0.745433789954338</v>
+        <v>0.7454337899543378</v>
       </c>
       <c r="F83" s="4" t="n">
         <v>653</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.208904109589041</v>
+        <v>0.2089041095890411</v>
       </c>
       <c r="H83" s="4" t="n">
         <v>183</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.00342465753424658</v>
+        <v>0.003424657534246575</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>3</v>
@@ -4242,19 +4242,19 @@
         </is>
       </c>
       <c r="C84" s="3" t="n">
-        <v>0.0202578268876611</v>
+        <v>0.02025782688766114</v>
       </c>
       <c r="D84" s="4" t="n">
         <v>11</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>0.5119705340699821</v>
+        <v>0.5119705340699816</v>
       </c>
       <c r="F84" s="4" t="n">
         <v>278</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.449355432780847</v>
+        <v>0.4493554327808472</v>
       </c>
       <c r="H84" s="4" t="n">
         <v>244</v>
@@ -4287,25 +4287,25 @@
         </is>
       </c>
       <c r="C85" s="3" t="n">
-        <v>0.186495176848875</v>
+        <v>0.1864951768488746</v>
       </c>
       <c r="D85" s="4" t="n">
         <v>174</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>0.190782422293676</v>
+        <v>0.1907824222936763</v>
       </c>
       <c r="F85" s="4" t="n">
         <v>178</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.558413719185423</v>
+        <v>0.5584137191854234</v>
       </c>
       <c r="H85" s="4" t="n">
         <v>521</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.0439442658092176</v>
+        <v>0.04394426580921758</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>41</v>
@@ -4332,19 +4332,19 @@
         </is>
       </c>
       <c r="C86" s="3" t="n">
-        <v>0.105022831050228</v>
+        <v>0.1050228310502283</v>
       </c>
       <c r="D86" s="4" t="n">
         <v>69</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>0.503805175038052</v>
+        <v>0.5038051750380518</v>
       </c>
       <c r="F86" s="4" t="n">
         <v>331</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.36986301369863</v>
+        <v>0.3698630136986301</v>
       </c>
       <c r="H86" s="4" t="n">
         <v>243</v>
@@ -4389,7 +4389,7 @@
         <v>120</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.441333333333333</v>
+        <v>0.4413333333333334</v>
       </c>
       <c r="H87" s="4" t="n">
         <v>331</v>
@@ -4422,25 +4422,25 @@
         </is>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0.255489021956088</v>
+        <v>0.2554890219560878</v>
       </c>
       <c r="D88" s="4" t="n">
         <v>128</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0.139720558882236</v>
+        <v>0.1397205588822355</v>
       </c>
       <c r="F88" s="4" t="n">
         <v>70</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.580838323353293</v>
+        <v>0.5808383233532934</v>
       </c>
       <c r="H88" s="4" t="n">
         <v>291</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.00598802395209581</v>
+        <v>0.005988023952095809</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>3</v>
@@ -4467,25 +4467,25 @@
         </is>
       </c>
       <c r="C89" s="3" t="n">
-        <v>0.168831168831169</v>
+        <v>0.1688311688311688</v>
       </c>
       <c r="D89" s="4" t="n">
         <v>65</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>0.483116883116883</v>
+        <v>0.4831168831168831</v>
       </c>
       <c r="F89" s="4" t="n">
         <v>186</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>0.316883116883117</v>
+        <v>0.3168831168831169</v>
       </c>
       <c r="H89" s="4" t="n">
         <v>122</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.0025974025974026</v>
+        <v>0.002597402597402597</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>1</v>
@@ -4512,25 +4512,25 @@
         </is>
       </c>
       <c r="C90" s="3" t="n">
-        <v>0.114597544338336</v>
+        <v>0.1145975443383356</v>
       </c>
       <c r="D90" s="4" t="n">
         <v>84</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>0.493860845839018</v>
+        <v>0.4938608458390177</v>
       </c>
       <c r="F90" s="4" t="n">
         <v>362</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.377899045020464</v>
+        <v>0.3778990450204638</v>
       </c>
       <c r="H90" s="4" t="n">
         <v>277</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.00136425648021828</v>
+        <v>0.001364256480218281</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>1</v>
@@ -4563,7 +4563,7 @@
         <v>184</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0.157360406091371</v>
+        <v>0.1573604060913706</v>
       </c>
       <c r="F91" s="4" t="n">
         <v>93</v>
@@ -4575,7 +4575,7 @@
         <v>292</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.00169204737732657</v>
+        <v>0.001692047377326565</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>1</v>
@@ -4602,19 +4602,19 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.222816399286987</v>
+        <v>0.2228163992869875</v>
       </c>
       <c r="D92" s="4" t="n">
         <v>125</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.0730837789661319</v>
+        <v>0.07308377896613191</v>
       </c>
       <c r="F92" s="4" t="n">
         <v>41</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.684491978609626</v>
+        <v>0.6844919786096256</v>
       </c>
       <c r="H92" s="4" t="n">
         <v>384</v>
@@ -4647,25 +4647,25 @@
         </is>
       </c>
       <c r="C93" s="3" t="n">
-        <v>0.305232558139535</v>
+        <v>0.3052325581395349</v>
       </c>
       <c r="D93" s="4" t="n">
         <v>210</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>0.318313953488372</v>
+        <v>0.3183139534883721</v>
       </c>
       <c r="F93" s="4" t="n">
         <v>219</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.36046511627907</v>
+        <v>0.3604651162790697</v>
       </c>
       <c r="H93" s="4" t="n">
         <v>248</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.00581395348837209</v>
+        <v>0.005813953488372093</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>4</v>
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="C94" s="3" t="n">
-        <v>0.374429223744292</v>
+        <v>0.3744292237442922</v>
       </c>
       <c r="D94" s="4" t="n">
         <v>246</v>
@@ -4704,7 +4704,7 @@
         <v>6</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.598173515981735</v>
+        <v>0.5981735159817352</v>
       </c>
       <c r="H94" s="4" t="n">
         <v>393</v>
@@ -4737,13 +4737,13 @@
         </is>
       </c>
       <c r="C95" s="3" t="n">
-        <v>0.0704225352112676</v>
+        <v>0.07042253521126761</v>
       </c>
       <c r="D95" s="4" t="n">
         <v>35</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>0.183098591549296</v>
+        <v>0.1830985915492958</v>
       </c>
       <c r="F95" s="4" t="n">
         <v>91</v>
@@ -4782,25 +4782,25 @@
         </is>
       </c>
       <c r="C96" s="3" t="n">
-        <v>0.233743409490334</v>
+        <v>0.2337434094903339</v>
       </c>
       <c r="D96" s="4" t="n">
         <v>133</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>0.00175746924428823</v>
+        <v>0.001757469244288225</v>
       </c>
       <c r="F96" s="4" t="n">
         <v>1</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.72231985940246</v>
+        <v>0.7223198594024605</v>
       </c>
       <c r="H96" s="4" t="n">
         <v>411</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.0228471001757469</v>
+        <v>0.02284710017574693</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>13</v>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="C97" s="3" t="n">
-        <v>0.308022922636103</v>
+        <v>0.3080229226361031</v>
       </c>
       <c r="D97" s="4" t="n">
         <v>215</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>0.00286532951289398</v>
+        <v>0.002865329512893983</v>
       </c>
       <c r="F97" s="4" t="n">
         <v>2</v>
@@ -4845,7 +4845,7 @@
         <v>462</v>
       </c>
       <c r="I97" s="3" t="n">
-        <v>0.0100286532951289</v>
+        <v>0.01002865329512894</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>7</v>
@@ -4872,19 +4872,19 @@
         </is>
       </c>
       <c r="C98" s="3" t="n">
-        <v>0.14410480349345</v>
+        <v>0.1441048034934498</v>
       </c>
       <c r="D98" s="4" t="n">
         <v>66</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>0.00655021834061135</v>
+        <v>0.006550218340611353</v>
       </c>
       <c r="F98" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>0.792576419213974</v>
+        <v>0.7925764192139738</v>
       </c>
       <c r="H98" s="4" t="n">
         <v>363</v>
@@ -4917,13 +4917,13 @@
         </is>
       </c>
       <c r="C99" s="3" t="n">
-        <v>0.371212121212121</v>
+        <v>0.3712121212121212</v>
       </c>
       <c r="D99" s="4" t="n">
         <v>245</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>0.00606060606060606</v>
+        <v>0.006060606060606061</v>
       </c>
       <c r="F99" s="4" t="n">
         <v>4</v>
@@ -4935,7 +4935,7 @@
         <v>392</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>0.00606060606060606</v>
+        <v>0.006060606060606061</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>4</v>
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0.27007299270073</v>
+        <v>0.2700729927007299</v>
       </c>
       <c r="D100" s="4" t="n">
         <v>185</v>
@@ -4974,7 +4974,7 @@
         <v>4</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0.696350364963504</v>
+        <v>0.6963503649635037</v>
       </c>
       <c r="H100" s="4" t="n">
         <v>477</v>
@@ -5007,25 +5007,25 @@
         </is>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0.227508650519031</v>
+        <v>0.2275086505190311</v>
       </c>
       <c r="D101" s="4" t="n">
         <v>263</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0.0069204152249135</v>
+        <v>0.006920415224913495</v>
       </c>
       <c r="F101" s="4" t="n">
         <v>8</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0.7283737024221451</v>
+        <v>0.7283737024221453</v>
       </c>
       <c r="H101" s="4" t="n">
         <v>842</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0.0069204152249135</v>
+        <v>0.006920415224913495</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>8</v>
@@ -5052,25 +5052,25 @@
         </is>
       </c>
       <c r="C102" s="3" t="n">
-        <v>0.44100580270793</v>
+        <v>0.4410058027079304</v>
       </c>
       <c r="D102" s="4" t="n">
         <v>228</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>0.00386847195357834</v>
+        <v>0.003868471953578337</v>
       </c>
       <c r="F102" s="4" t="n">
         <v>2</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>0.531914893617021</v>
+        <v>0.5319148936170213</v>
       </c>
       <c r="H102" s="4" t="n">
         <v>275</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>0.00193423597678917</v>
+        <v>0.001934235976789168</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>1</v>
@@ -5103,19 +5103,19 @@
         <v>200</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0.132516703786191</v>
+        <v>0.1325167037861915</v>
       </c>
       <c r="F103" s="4" t="n">
         <v>119</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0.602449888641425</v>
+        <v>0.6024498886414253</v>
       </c>
       <c r="H103" s="4" t="n">
         <v>541</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0.0256124721603563</v>
+        <v>0.02561247216035635</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>23</v>
@@ -5142,25 +5142,25 @@
         </is>
       </c>
       <c r="C104" s="3" t="n">
-        <v>0.343283582089552</v>
+        <v>0.3432835820895522</v>
       </c>
       <c r="D104" s="4" t="n">
         <v>230</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>0.0597014925373134</v>
+        <v>0.05970149253731343</v>
       </c>
       <c r="F104" s="4" t="n">
         <v>40</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>0.5791044776119399</v>
+        <v>0.5791044776119403</v>
       </c>
       <c r="H104" s="4" t="n">
         <v>388</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>0.00447761194029851</v>
+        <v>0.004477611940298508</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>3</v>
@@ -5187,25 +5187,25 @@
         </is>
       </c>
       <c r="C105" s="3" t="n">
-        <v>0.248275862068965</v>
+        <v>0.2482758620689655</v>
       </c>
       <c r="D105" s="4" t="n">
         <v>108</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>0.257471264367816</v>
+        <v>0.2574712643678161</v>
       </c>
       <c r="F105" s="4" t="n">
         <v>112</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>0.471264367816092</v>
+        <v>0.4712643678160919</v>
       </c>
       <c r="H105" s="4" t="n">
         <v>205</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>0.00689655172413793</v>
+        <v>0.006896551724137931</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>3</v>
@@ -5232,25 +5232,25 @@
         </is>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.218967921896792</v>
+        <v>0.2189679218967922</v>
       </c>
       <c r="D106" s="4" t="n">
         <v>157</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.185495118549512</v>
+        <v>0.1854951185495119</v>
       </c>
       <c r="F106" s="4" t="n">
         <v>133</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.574616457461646</v>
+        <v>0.5746164574616457</v>
       </c>
       <c r="H106" s="4" t="n">
         <v>412</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.00418410041841004</v>
+        <v>0.004184100418410041</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>3</v>
@@ -5277,19 +5277,19 @@
         </is>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0.408829174664108</v>
+        <v>0.4088291746641075</v>
       </c>
       <c r="D107" s="4" t="n">
         <v>213</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0.0287907869481766</v>
+        <v>0.02879078694817658</v>
       </c>
       <c r="F107" s="4" t="n">
         <v>15</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0.53742802303263</v>
+        <v>0.5374280230326296</v>
       </c>
       <c r="H107" s="4" t="n">
         <v>280</v>
@@ -5322,25 +5322,25 @@
         </is>
       </c>
       <c r="C108" s="3" t="n">
-        <v>0.271337579617834</v>
+        <v>0.2713375796178344</v>
       </c>
       <c r="D108" s="4" t="n">
         <v>213</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>0.0191082802547771</v>
+        <v>0.01910828025477707</v>
       </c>
       <c r="F108" s="4" t="n">
         <v>15</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>0.64968152866242</v>
+        <v>0.6496815286624203</v>
       </c>
       <c r="H108" s="4" t="n">
         <v>510</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>0.0292993630573248</v>
+        <v>0.02929936305732484</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>23</v>
@@ -5367,25 +5367,25 @@
         </is>
       </c>
       <c r="C109" s="3" t="n">
-        <v>0.342013888888889</v>
+        <v>0.3420138888888889</v>
       </c>
       <c r="D109" s="4" t="n">
         <v>197</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>0.0243055555555556</v>
+        <v>0.02430555555555556</v>
       </c>
       <c r="F109" s="4" t="n">
         <v>14</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>0.607638888888889</v>
+        <v>0.6076388888888888</v>
       </c>
       <c r="H109" s="4" t="n">
         <v>350</v>
       </c>
       <c r="I109" s="3" t="n">
-        <v>0.0121527777777778</v>
+        <v>0.01215277777777778</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>7</v>
@@ -5412,19 +5412,19 @@
         </is>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0.432216905901116</v>
+        <v>0.4322169059011164</v>
       </c>
       <c r="D110" s="4" t="n">
         <v>271</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0.0143540669856459</v>
+        <v>0.01435406698564593</v>
       </c>
       <c r="F110" s="4" t="n">
         <v>9</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0.524720893141946</v>
+        <v>0.5247208931419458</v>
       </c>
       <c r="H110" s="4" t="n">
         <v>329</v>
@@ -5457,13 +5457,13 @@
         </is>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0.406451612903226</v>
+        <v>0.4064516129032258</v>
       </c>
       <c r="D111" s="4" t="n">
         <v>189</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0.0021505376344086</v>
+        <v>0.002150537634408602</v>
       </c>
       <c r="F111" s="4" t="n">
         <v>1</v>
@@ -5475,7 +5475,7 @@
         <v>264</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0.00645161290322581</v>
+        <v>0.006451612903225806</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>3</v>
@@ -5502,25 +5502,25 @@
         </is>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0.441489361702128</v>
+        <v>0.4414893617021277</v>
       </c>
       <c r="D112" s="4" t="n">
         <v>332</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0.00265957446808511</v>
+        <v>0.002659574468085106</v>
       </c>
       <c r="F112" s="4" t="n">
         <v>2</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0.509308510638298</v>
+        <v>0.5093085106382979</v>
       </c>
       <c r="H112" s="4" t="n">
         <v>383</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0.00930851063829787</v>
+        <v>0.009308510638297872</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>7</v>
@@ -5547,25 +5547,25 @@
         </is>
       </c>
       <c r="C113" s="3" t="n">
-        <v>0.397783251231527</v>
+        <v>0.3977832512315271</v>
       </c>
       <c r="D113" s="4" t="n">
         <v>323</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>0.00985221674876847</v>
+        <v>0.009852216748768473</v>
       </c>
       <c r="F113" s="4" t="n">
         <v>8</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>0.549261083743842</v>
+        <v>0.5492610837438424</v>
       </c>
       <c r="H113" s="4" t="n">
         <v>446</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>0.0123152709359606</v>
+        <v>0.01231527093596059</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>10</v>
@@ -5592,25 +5592,25 @@
         </is>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0.0161662817551963</v>
+        <v>0.01616628175519631</v>
       </c>
       <c r="D114" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0.900692840646651</v>
+        <v>0.9006928406466512</v>
       </c>
       <c r="F114" s="4" t="n">
         <v>390</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0.0715935334872979</v>
+        <v>0.07159353348729793</v>
       </c>
       <c r="H114" s="4" t="n">
         <v>31</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>0.0023094688221709</v>
+        <v>0.002309468822170901</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>1</v>
@@ -5637,19 +5637,19 @@
         </is>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0.278761061946903</v>
+        <v>0.2787610619469026</v>
       </c>
       <c r="D115" s="4" t="n">
         <v>315</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0.201769911504425</v>
+        <v>0.2017699115044248</v>
       </c>
       <c r="F115" s="4" t="n">
         <v>228</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0.492920353982301</v>
+        <v>0.4929203539823009</v>
       </c>
       <c r="H115" s="4" t="n">
         <v>557</v>
@@ -5682,13 +5682,13 @@
         </is>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0.225037257824143</v>
+        <v>0.2250372578241431</v>
       </c>
       <c r="D116" s="4" t="n">
         <v>151</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0.178837555886736</v>
+        <v>0.1788375558867362</v>
       </c>
       <c r="F116" s="4" t="n">
         <v>120</v>
@@ -5700,7 +5700,7 @@
         <v>378</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0.0104321907600596</v>
+        <v>0.01043219076005961</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>7</v>
@@ -5727,25 +5727,25 @@
         </is>
       </c>
       <c r="C117" s="3" t="n">
-        <v>0.56793893129771</v>
+        <v>0.5679389312977099</v>
       </c>
       <c r="D117" s="4" t="n">
         <v>372</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>0.00610687022900763</v>
+        <v>0.006106870229007634</v>
       </c>
       <c r="F117" s="4" t="n">
         <v>4</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>0.409160305343511</v>
+        <v>0.4091603053435114</v>
       </c>
       <c r="H117" s="4" t="n">
         <v>268</v>
       </c>
       <c r="I117" s="3" t="n">
-        <v>0.00610687022900763</v>
+        <v>0.006106870229007634</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>4</v>
@@ -5778,7 +5778,7 @@
         <v>440</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.00530503978779841</v>
+        <v>0.005305039787798408</v>
       </c>
       <c r="F118" s="4" t="n">
         <v>4</v>
@@ -5790,7 +5790,7 @@
         <v>299</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.00530503978779841</v>
+        <v>0.005305039787798408</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>4</v>
@@ -5823,19 +5823,19 @@
         <v>443</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>0.00393184796854522</v>
+        <v>0.003931847968545216</v>
       </c>
       <c r="F119" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>0.374836173001311</v>
+        <v>0.3748361730013106</v>
       </c>
       <c r="H119" s="4" t="n">
         <v>286</v>
       </c>
       <c r="I119" s="3" t="n">
-        <v>0.0117955439056357</v>
+        <v>0.01179554390563565</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>9</v>
@@ -5862,25 +5862,25 @@
         </is>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0.217465753424657</v>
+        <v>0.2174657534246575</v>
       </c>
       <c r="D120" s="4" t="n">
         <v>127</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0.0428082191780822</v>
+        <v>0.04280821917808219</v>
       </c>
       <c r="F120" s="4" t="n">
         <v>25</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0.703767123287671</v>
+        <v>0.7037671232876712</v>
       </c>
       <c r="H120" s="4" t="n">
         <v>411</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>0.00513698630136986</v>
+        <v>0.005136986301369863</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>3</v>
@@ -5907,25 +5907,25 @@
         </is>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0.23952738990333</v>
+        <v>0.2395273899033298</v>
       </c>
       <c r="D121" s="4" t="n">
         <v>223</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0.0773361976369495</v>
+        <v>0.07733619763694952</v>
       </c>
       <c r="F121" s="4" t="n">
         <v>72</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0.638023630504833</v>
+        <v>0.6380236305048335</v>
       </c>
       <c r="H121" s="4" t="n">
         <v>594</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0.0182599355531686</v>
+        <v>0.01825993555316864</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>17</v>
@@ -5952,7 +5952,7 @@
         </is>
       </c>
       <c r="C122" s="3" t="n">
-        <v>0.34115523465704</v>
+        <v>0.3411552346570397</v>
       </c>
       <c r="D122" s="4" t="n">
         <v>189</v>
@@ -5964,13 +5964,13 @@
         <v>0</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>0.6119133574007219</v>
+        <v>0.6119133574007221</v>
       </c>
       <c r="H122" s="4" t="n">
         <v>339</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>0.0324909747292419</v>
+        <v>0.03249097472924187</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>18</v>
@@ -5997,25 +5997,25 @@
         </is>
       </c>
       <c r="C123" s="3" t="n">
-        <v>0.18218085106383</v>
+        <v>0.1821808510638298</v>
       </c>
       <c r="D123" s="4" t="n">
         <v>137</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>0.0159574468085106</v>
+        <v>0.01595744680851064</v>
       </c>
       <c r="F123" s="4" t="n">
         <v>12</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>0.75531914893617</v>
+        <v>0.7553191489361702</v>
       </c>
       <c r="H123" s="4" t="n">
         <v>568</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>0.00930851063829787</v>
+        <v>0.009308510638297872</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>7</v>
@@ -6042,25 +6042,25 @@
         </is>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0.368800721370604</v>
+        <v>0.3688007213706042</v>
       </c>
       <c r="D124" s="4" t="n">
         <v>409</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0.0117222723174031</v>
+        <v>0.01172227231740307</v>
       </c>
       <c r="F124" s="4" t="n">
         <v>13</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0.596934174932372</v>
+        <v>0.5969341749323716</v>
       </c>
       <c r="H124" s="4" t="n">
         <v>662</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0.0036068530207394</v>
+        <v>0.003606853020739405</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>4</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0.419064748201439</v>
+        <v>0.4190647482014389</v>
       </c>
       <c r="D125" s="4" t="n">
         <v>233</v>
@@ -6099,13 +6099,13 @@
         <v>0</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0.557553956834532</v>
+        <v>0.5575539568345323</v>
       </c>
       <c r="H125" s="4" t="n">
         <v>310</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0.00719424460431655</v>
+        <v>0.007194244604316547</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>4</v>
@@ -6132,25 +6132,25 @@
         </is>
       </c>
       <c r="C126" s="3" t="n">
-        <v>0.463551401869159</v>
+        <v>0.4635514018691589</v>
       </c>
       <c r="D126" s="4" t="n">
         <v>248</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>0.00560747663551402</v>
+        <v>0.005607476635514018</v>
       </c>
       <c r="F126" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>0.51214953271028</v>
+        <v>0.5121495327102804</v>
       </c>
       <c r="H126" s="4" t="n">
         <v>274</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>0.00747663551401869</v>
+        <v>0.007476635514018692</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>4</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="C127" s="3" t="n">
-        <v>0.355140186915888</v>
+        <v>0.3551401869158878</v>
       </c>
       <c r="D127" s="4" t="n">
         <v>152</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>0.00934579439252336</v>
+        <v>0.009345794392523364</v>
       </c>
       <c r="F127" s="4" t="n">
         <v>4</v>
@@ -6195,7 +6195,7 @@
         <v>258</v>
       </c>
       <c r="I127" s="3" t="n">
-        <v>0.0116822429906542</v>
+        <v>0.01168224299065421</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>5</v>
@@ -6222,25 +6222,25 @@
         </is>
       </c>
       <c r="C128" s="3" t="n">
-        <v>0.319715808170515</v>
+        <v>0.3197158081705151</v>
       </c>
       <c r="D128" s="4" t="n">
         <v>180</v>
       </c>
       <c r="E128" s="3" t="n">
-        <v>0.0568383658969805</v>
+        <v>0.05683836589698046</v>
       </c>
       <c r="F128" s="4" t="n">
         <v>32</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>0.575488454706927</v>
+        <v>0.5754884547069272</v>
       </c>
       <c r="H128" s="4" t="n">
         <v>324</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>0.0159857904085258</v>
+        <v>0.01598579040852575</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>9</v>
@@ -6267,7 +6267,7 @@
         </is>
       </c>
       <c r="C129" s="3" t="n">
-        <v>0.404761904761905</v>
+        <v>0.4047619047619048</v>
       </c>
       <c r="D129" s="4" t="n">
         <v>442</v>
@@ -6279,13 +6279,13 @@
         <v>13</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>0.547619047619048</v>
+        <v>0.5476190476190477</v>
       </c>
       <c r="H129" s="4" t="n">
         <v>598</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>0.0100732600732601</v>
+        <v>0.01007326007326007</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>11</v>
@@ -6312,25 +6312,25 @@
         </is>
       </c>
       <c r="C130" s="3" t="n">
-        <v>0.405257393209201</v>
+        <v>0.4052573932092005</v>
       </c>
       <c r="D130" s="4" t="n">
         <v>370</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>0.0142387732749179</v>
+        <v>0.01423877327491785</v>
       </c>
       <c r="F130" s="4" t="n">
         <v>13</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>0.537787513691128</v>
+        <v>0.5377875136911281</v>
       </c>
       <c r="H130" s="4" t="n">
         <v>491</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>0.0197152245345016</v>
+        <v>0.01971522453450164</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>18</v>
@@ -6357,19 +6357,19 @@
         </is>
       </c>
       <c r="C131" s="3" t="n">
-        <v>0.261390887290168</v>
+        <v>0.2613908872901679</v>
       </c>
       <c r="D131" s="4" t="n">
         <v>109</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>0.0143884892086331</v>
+        <v>0.01438848920863309</v>
       </c>
       <c r="F131" s="4" t="n">
         <v>6</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>0.707434052757794</v>
+        <v>0.7074340527577938</v>
       </c>
       <c r="H131" s="4" t="n">
         <v>295</v>
@@ -6402,13 +6402,13 @@
         </is>
       </c>
       <c r="C132" s="3" t="n">
-        <v>0.273809523809524</v>
+        <v>0.2738095238095238</v>
       </c>
       <c r="D132" s="4" t="n">
         <v>276</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>0.201388888888889</v>
+        <v>0.2013888888888889</v>
       </c>
       <c r="F132" s="4" t="n">
         <v>203</v>
@@ -6420,7 +6420,7 @@
         <v>506</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>0.00595238095238095</v>
+        <v>0.005952380952380952</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>6</v>
@@ -6447,25 +6447,25 @@
         </is>
       </c>
       <c r="C133" s="3" t="n">
-        <v>0.466960352422908</v>
+        <v>0.4669603524229075</v>
       </c>
       <c r="D133" s="4" t="n">
         <v>318</v>
       </c>
       <c r="E133" s="3" t="n">
-        <v>0.0102790014684288</v>
+        <v>0.01027900146842878</v>
       </c>
       <c r="F133" s="4" t="n">
         <v>7</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>0.500734214390602</v>
+        <v>0.5007342143906021</v>
       </c>
       <c r="H133" s="4" t="n">
         <v>341</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>0.00146842878120411</v>
+        <v>0.001468428781204112</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>1</v>
@@ -6492,19 +6492,19 @@
         </is>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0.179245283018868</v>
+        <v>0.1792452830188679</v>
       </c>
       <c r="D134" s="4" t="n">
         <v>95</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0.00566037735849057</v>
+        <v>0.005660377358490566</v>
       </c>
       <c r="F134" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0.80377358490566</v>
+        <v>0.8037735849056604</v>
       </c>
       <c r="H134" s="4" t="n">
         <v>426</v>
@@ -6537,25 +6537,25 @@
         </is>
       </c>
       <c r="C135" s="3" t="n">
-        <v>0.253943217665615</v>
+        <v>0.2539432176656151</v>
       </c>
       <c r="D135" s="4" t="n">
         <v>161</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>0.0141955835962145</v>
+        <v>0.01419558359621451</v>
       </c>
       <c r="F135" s="4" t="n">
         <v>9</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>0.706624605678234</v>
+        <v>0.7066246056782335</v>
       </c>
       <c r="H135" s="4" t="n">
         <v>448</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>0.00630914826498423</v>
+        <v>0.006309148264984227</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>4</v>
@@ -6582,25 +6582,25 @@
         </is>
       </c>
       <c r="C136" s="3" t="n">
-        <v>0.0648148148148148</v>
+        <v>0.06481481481481481</v>
       </c>
       <c r="D136" s="4" t="n">
         <v>28</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>0.0115740740740741</v>
+        <v>0.01157407407407407</v>
       </c>
       <c r="F136" s="4" t="n">
         <v>5</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>0.895833333333333</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="H136" s="4" t="n">
         <v>387</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>0.00694444444444444</v>
+        <v>0.006944444444444444</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>3</v>
@@ -6627,7 +6627,7 @@
         </is>
       </c>
       <c r="C137" s="3" t="n">
-        <v>0.111498257839721</v>
+        <v>0.1114982578397213</v>
       </c>
       <c r="D137" s="4" t="n">
         <v>96</v>
@@ -6639,7 +6639,7 @@
         <v>10</v>
       </c>
       <c r="G137" s="3" t="n">
-        <v>0.855981416957027</v>
+        <v>0.8559814169570267</v>
       </c>
       <c r="H137" s="4" t="n">
         <v>737</v>
@@ -6672,19 +6672,19 @@
         </is>
       </c>
       <c r="C138" s="3" t="n">
-        <v>0.11830985915493</v>
+        <v>0.1183098591549296</v>
       </c>
       <c r="D138" s="4" t="n">
         <v>84</v>
       </c>
       <c r="E138" s="3" t="n">
-        <v>0.0253521126760563</v>
+        <v>0.02535211267605634</v>
       </c>
       <c r="F138" s="4" t="n">
         <v>18</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>0.832394366197183</v>
+        <v>0.8323943661971831</v>
       </c>
       <c r="H138" s="4" t="n">
         <v>591</v>
@@ -6717,25 +6717,25 @@
         </is>
       </c>
       <c r="C139" s="3" t="n">
-        <v>0.353391684901532</v>
+        <v>0.3533916849015317</v>
       </c>
       <c r="D139" s="4" t="n">
         <v>323</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>0.289934354485777</v>
+        <v>0.2899343544857768</v>
       </c>
       <c r="F139" s="4" t="n">
         <v>265</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>0.336980306345733</v>
+        <v>0.3369803063457331</v>
       </c>
       <c r="H139" s="4" t="n">
         <v>308</v>
       </c>
       <c r="I139" s="3" t="n">
-        <v>0.00218818380743982</v>
+        <v>0.002188183807439825</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>2</v>
@@ -6762,19 +6762,19 @@
         </is>
       </c>
       <c r="C140" s="3" t="n">
-        <v>0.0607594936708861</v>
+        <v>0.06075949367088607</v>
       </c>
       <c r="D140" s="4" t="n">
         <v>24</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>0.736708860759494</v>
+        <v>0.7367088607594937</v>
       </c>
       <c r="F140" s="4" t="n">
         <v>291</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>0.194936708860759</v>
+        <v>0.1949367088607595</v>
       </c>
       <c r="H140" s="4" t="n">
         <v>77</v>
@@ -6807,25 +6807,25 @@
         </is>
       </c>
       <c r="C141" s="3" t="n">
-        <v>0.244781783681214</v>
+        <v>0.2447817836812144</v>
       </c>
       <c r="D141" s="4" t="n">
         <v>129</v>
       </c>
       <c r="E141" s="3" t="n">
-        <v>0.358633776091082</v>
+        <v>0.3586337760910816</v>
       </c>
       <c r="F141" s="4" t="n">
         <v>189</v>
       </c>
       <c r="G141" s="3" t="n">
-        <v>0.370018975332068</v>
+        <v>0.3700189753320683</v>
       </c>
       <c r="H141" s="4" t="n">
         <v>195</v>
       </c>
       <c r="I141" s="3" t="n">
-        <v>0.00759013282732448</v>
+        <v>0.007590132827324478</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>4</v>
@@ -6858,13 +6858,13 @@
         <v>14</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>0.6209048361934481</v>
+        <v>0.6209048361934477</v>
       </c>
       <c r="F142" s="4" t="n">
         <v>398</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>0.341653666146646</v>
+        <v>0.3416536661466459</v>
       </c>
       <c r="H142" s="4" t="n">
         <v>219</v>
@@ -6897,25 +6897,25 @@
         </is>
       </c>
       <c r="C143" s="3" t="n">
-        <v>0.0251655629139073</v>
+        <v>0.02516556291390729</v>
       </c>
       <c r="D143" s="4" t="n">
         <v>19</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>0.6476821192052979</v>
+        <v>0.6476821192052981</v>
       </c>
       <c r="F143" s="4" t="n">
         <v>489</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>0.31523178807947</v>
+        <v>0.3152317880794702</v>
       </c>
       <c r="H143" s="4" t="n">
         <v>238</v>
       </c>
       <c r="I143" s="3" t="n">
-        <v>0.00264900662251656</v>
+        <v>0.002649006622516556</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>2</v>
@@ -6942,7 +6942,7 @@
         </is>
       </c>
       <c r="C144" s="3" t="n">
-        <v>0.0133868808567604</v>
+        <v>0.01338688085676037</v>
       </c>
       <c r="D144" s="4" t="n">
         <v>10</v>
@@ -6954,13 +6954,13 @@
         <v>613</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>0.153949129852744</v>
+        <v>0.1539491298527443</v>
       </c>
       <c r="H144" s="4" t="n">
         <v>115</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>0.00267737617135207</v>
+        <v>0.002677376171352075</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>2</v>
@@ -6987,19 +6987,19 @@
         </is>
       </c>
       <c r="C145" s="3" t="n">
-        <v>0.181543116490166</v>
+        <v>0.1815431164901664</v>
       </c>
       <c r="D145" s="4" t="n">
         <v>120</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>0.009077155824508319</v>
+        <v>0.009077155824508321</v>
       </c>
       <c r="F145" s="4" t="n">
         <v>6</v>
       </c>
       <c r="G145" s="3" t="n">
-        <v>0.7745839636913771</v>
+        <v>0.7745839636913767</v>
       </c>
       <c r="H145" s="4" t="n">
         <v>512</v>
@@ -7032,13 +7032,13 @@
         </is>
       </c>
       <c r="C146" s="3" t="n">
-        <v>0.319852941176471</v>
+        <v>0.3198529411764706</v>
       </c>
       <c r="D146" s="4" t="n">
         <v>261</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>0.0122549019607843</v>
+        <v>0.01225490196078431</v>
       </c>
       <c r="F146" s="4" t="n">
         <v>10</v>
@@ -7050,7 +7050,7 @@
         <v>510</v>
       </c>
       <c r="I146" s="3" t="n">
-        <v>0.00122549019607843</v>
+        <v>0.001225490196078431</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>1</v>
@@ -7077,25 +7077,25 @@
         </is>
       </c>
       <c r="C147" s="3" t="n">
-        <v>0.255813953488372</v>
+        <v>0.2558139534883721</v>
       </c>
       <c r="D147" s="4" t="n">
         <v>121</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>0.00634249471458774</v>
+        <v>0.006342494714587738</v>
       </c>
       <c r="F147" s="4" t="n">
         <v>3</v>
       </c>
       <c r="G147" s="3" t="n">
-        <v>0.725158562367865</v>
+        <v>0.7251585623678647</v>
       </c>
       <c r="H147" s="4" t="n">
         <v>343</v>
       </c>
       <c r="I147" s="3" t="n">
-        <v>0.00634249471458774</v>
+        <v>0.006342494714587738</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>3</v>
@@ -7122,13 +7122,13 @@
         </is>
       </c>
       <c r="C148" s="3" t="n">
-        <v>0.018887722980063</v>
+        <v>0.01888772298006296</v>
       </c>
       <c r="D148" s="4" t="n">
         <v>18</v>
       </c>
       <c r="E148" s="3" t="n">
-        <v>0.684155299055614</v>
+        <v>0.6841552990556139</v>
       </c>
       <c r="F148" s="4" t="n">
         <v>652</v>
@@ -7167,25 +7167,25 @@
         </is>
       </c>
       <c r="C149" s="3" t="n">
-        <v>0.0350877192982456</v>
+        <v>0.03508771929824561</v>
       </c>
       <c r="D149" s="4" t="n">
         <v>30</v>
       </c>
       <c r="E149" s="3" t="n">
-        <v>0.567251461988304</v>
+        <v>0.5672514619883041</v>
       </c>
       <c r="F149" s="4" t="n">
         <v>485</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>0.363742690058479</v>
+        <v>0.3637426900584795</v>
       </c>
       <c r="H149" s="4" t="n">
         <v>311</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>0.00701754385964912</v>
+        <v>0.007017543859649123</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>6</v>
@@ -7212,25 +7212,25 @@
         </is>
       </c>
       <c r="C150" s="3" t="n">
-        <v>0.10413694721826</v>
+        <v>0.1041369472182596</v>
       </c>
       <c r="D150" s="4" t="n">
         <v>73</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>0.0513552068473609</v>
+        <v>0.05135520684736091</v>
       </c>
       <c r="F150" s="4" t="n">
         <v>36</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>0.830242510699001</v>
+        <v>0.8302425106990015</v>
       </c>
       <c r="H150" s="4" t="n">
         <v>582</v>
       </c>
       <c r="I150" s="3" t="n">
-        <v>0.0014265335235378</v>
+        <v>0.001426533523537803</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>1</v>
@@ -7257,25 +7257,25 @@
         </is>
       </c>
       <c r="C151" s="3" t="n">
-        <v>0.0072463768115942</v>
+        <v>0.007246376811594203</v>
       </c>
       <c r="D151" s="4" t="n">
         <v>8</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>0.828804347826087</v>
+        <v>0.8288043478260869</v>
       </c>
       <c r="F151" s="4" t="n">
         <v>915</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>0.153985507246377</v>
+        <v>0.1539855072463768</v>
       </c>
       <c r="H151" s="4" t="n">
         <v>170</v>
       </c>
       <c r="I151" s="3" t="n">
-        <v>0.00181159420289855</v>
+        <v>0.001811594202898551</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>2</v>
@@ -7308,19 +7308,19 @@
         <v>32</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>0.512645914396887</v>
+        <v>0.5126459143968871</v>
       </c>
       <c r="F152" s="4" t="n">
         <v>527</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>0.440661478599222</v>
+        <v>0.4406614785992218</v>
       </c>
       <c r="H152" s="4" t="n">
         <v>453</v>
       </c>
       <c r="I152" s="3" t="n">
-        <v>0.00291828793774319</v>
+        <v>0.002918287937743191</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>3</v>
@@ -7347,25 +7347,25 @@
         </is>
       </c>
       <c r="C153" s="3" t="n">
-        <v>0.0207336523125997</v>
+        <v>0.02073365231259968</v>
       </c>
       <c r="D153" s="4" t="n">
         <v>13</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>0.629984051036683</v>
+        <v>0.6299840510366826</v>
       </c>
       <c r="F153" s="4" t="n">
         <v>395</v>
       </c>
       <c r="G153" s="3" t="n">
-        <v>0.325358851674641</v>
+        <v>0.3253588516746411</v>
       </c>
       <c r="H153" s="4" t="n">
         <v>204</v>
       </c>
       <c r="I153" s="3" t="n">
-        <v>0.00159489633173844</v>
+        <v>0.001594896331738437</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>1</v>
@@ -7392,25 +7392,25 @@
         </is>
       </c>
       <c r="C154" s="3" t="n">
-        <v>0.138888888888889</v>
+        <v>0.1388888888888889</v>
       </c>
       <c r="D154" s="4" t="n">
         <v>100</v>
       </c>
       <c r="E154" s="3" t="n">
-        <v>0.469444444444444</v>
+        <v>0.4694444444444444</v>
       </c>
       <c r="F154" s="4" t="n">
         <v>338</v>
       </c>
       <c r="G154" s="3" t="n">
-        <v>0.366666666666667</v>
+        <v>0.3666666666666666</v>
       </c>
       <c r="H154" s="4" t="n">
         <v>264</v>
       </c>
       <c r="I154" s="3" t="n">
-        <v>0.00555555555555556</v>
+        <v>0.005555555555555556</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>4</v>
@@ -7443,13 +7443,13 @@
         <v>20</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>0.7566909975669101</v>
+        <v>0.7566909975669099</v>
       </c>
       <c r="F155" s="4" t="n">
         <v>622</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>0.201946472019465</v>
+        <v>0.2019464720194647</v>
       </c>
       <c r="H155" s="4" t="n">
         <v>166</v>
@@ -7488,7 +7488,7 @@
         <v>7</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>0.685234305923961</v>
+        <v>0.6852343059239611</v>
       </c>
       <c r="F156" s="4" t="n">
         <v>775</v>
@@ -7500,7 +7500,7 @@
         <v>309</v>
       </c>
       <c r="I156" s="3" t="n">
-        <v>0.00442086648983201</v>
+        <v>0.004420866489832007</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>5</v>
@@ -7527,19 +7527,19 @@
         </is>
       </c>
       <c r="C157" s="3" t="n">
-        <v>0.06792452830188681</v>
+        <v>0.06792452830188679</v>
       </c>
       <c r="D157" s="4" t="n">
         <v>36</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>0.313207547169811</v>
+        <v>0.3132075471698113</v>
       </c>
       <c r="F157" s="4" t="n">
         <v>166</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>0.609433962264151</v>
+        <v>0.6094339622641509</v>
       </c>
       <c r="H157" s="4" t="n">
         <v>323</v>
@@ -7572,25 +7572,25 @@
         </is>
       </c>
       <c r="C158" s="3" t="n">
-        <v>0.00153139356814701</v>
+        <v>0.001531393568147014</v>
       </c>
       <c r="D158" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>0.822358346094946</v>
+        <v>0.8223583460949464</v>
       </c>
       <c r="F158" s="4" t="n">
         <v>537</v>
       </c>
       <c r="G158" s="3" t="n">
-        <v>0.169984686064319</v>
+        <v>0.1699846860643185</v>
       </c>
       <c r="H158" s="4" t="n">
         <v>111</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>0.00153139356814701</v>
+        <v>0.001531393568147014</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>1</v>
@@ -7623,19 +7623,19 @@
         <v>0</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>0.834239130434783</v>
+        <v>0.8342391304347826</v>
       </c>
       <c r="F159" s="4" t="n">
         <v>307</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>0.146739130434783</v>
+        <v>0.1467391304347826</v>
       </c>
       <c r="H159" s="4" t="n">
         <v>54</v>
       </c>
       <c r="I159" s="3" t="n">
-        <v>0.00271739130434783</v>
+        <v>0.002717391304347826</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>1</v>
@@ -7662,25 +7662,25 @@
         </is>
       </c>
       <c r="C160" s="3" t="n">
-        <v>0.00091743119266055</v>
+        <v>0.0009174311926605505</v>
       </c>
       <c r="D160" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>0.596330275229358</v>
+        <v>0.5963302752293578</v>
       </c>
       <c r="F160" s="4" t="n">
         <v>650</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>0.398165137614679</v>
+        <v>0.3981651376146789</v>
       </c>
       <c r="H160" s="4" t="n">
         <v>434</v>
       </c>
       <c r="I160" s="3" t="n">
-        <v>0.00091743119266055</v>
+        <v>0.0009174311926605505</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>1</v>
@@ -7707,25 +7707,25 @@
         </is>
       </c>
       <c r="C161" s="3" t="n">
-        <v>0.00892857142857143</v>
+        <v>0.008928571428571428</v>
       </c>
       <c r="D161" s="4" t="n">
         <v>6</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>0.602678571428571</v>
+        <v>0.6026785714285714</v>
       </c>
       <c r="F161" s="4" t="n">
         <v>405</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>0.366071428571428</v>
+        <v>0.3660714285714285</v>
       </c>
       <c r="H161" s="4" t="n">
         <v>246</v>
       </c>
       <c r="I161" s="3" t="n">
-        <v>0.00446428571428571</v>
+        <v>0.004464285714285714</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>3</v>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="C162" s="3" t="n">
-        <v>0.0012987012987013</v>
+        <v>0.001298701298701299</v>
       </c>
       <c r="D162" s="4" t="n">
         <v>1</v>
@@ -7764,13 +7764,13 @@
         <v>492</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>0.348051948051948</v>
+        <v>0.3480519480519481</v>
       </c>
       <c r="H162" s="4" t="n">
         <v>268</v>
       </c>
       <c r="I162" s="3" t="n">
-        <v>0.0012987012987013</v>
+        <v>0.001298701298701299</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>1</v>
@@ -7797,19 +7797,19 @@
         </is>
       </c>
       <c r="C163" s="3" t="n">
-        <v>0.0122494432071269</v>
+        <v>0.01224944320712695</v>
       </c>
       <c r="D163" s="4" t="n">
         <v>11</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>0.561247216035635</v>
+        <v>0.5612472160356348</v>
       </c>
       <c r="F163" s="4" t="n">
         <v>504</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>0.417594654788419</v>
+        <v>0.4175946547884187</v>
       </c>
       <c r="H163" s="4" t="n">
         <v>375</v>
@@ -7842,13 +7842,13 @@
         </is>
       </c>
       <c r="C164" s="3" t="n">
-        <v>0.104417670682731</v>
+        <v>0.1044176706827309</v>
       </c>
       <c r="D164" s="4" t="n">
         <v>78</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>0.772423025435074</v>
+        <v>0.7724230254350736</v>
       </c>
       <c r="F164" s="4" t="n">
         <v>577</v>
@@ -7860,7 +7860,7 @@
         <v>81</v>
       </c>
       <c r="I164" s="3" t="n">
-        <v>0.00133868808567604</v>
+        <v>0.001338688085676037</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>1</v>
@@ -7887,25 +7887,25 @@
         </is>
       </c>
       <c r="C165" s="3" t="n">
-        <v>0.0212314225053078</v>
+        <v>0.02123142250530785</v>
       </c>
       <c r="D165" s="4" t="n">
         <v>10</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>0.273885350318471</v>
+        <v>0.2738853503184713</v>
       </c>
       <c r="F165" s="4" t="n">
         <v>129</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>0.679405520169851</v>
+        <v>0.6794055201698513</v>
       </c>
       <c r="H165" s="4" t="n">
         <v>320</v>
       </c>
       <c r="I165" s="3" t="n">
-        <v>0.00849256900212314</v>
+        <v>0.008492569002123142</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>4</v>
@@ -7989,13 +7989,13 @@
         <v>147</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>0.710714285714286</v>
+        <v>0.7107142857142857</v>
       </c>
       <c r="H167" s="4" t="n">
         <v>398</v>
       </c>
       <c r="I167" s="3" t="n">
-        <v>0.00178571428571429</v>
+        <v>0.001785714285714286</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>1</v>
@@ -8022,19 +8022,19 @@
         </is>
       </c>
       <c r="C168" s="3" t="n">
-        <v>0.0013351134846462</v>
+        <v>0.001335113484646195</v>
       </c>
       <c r="D168" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E168" s="3" t="n">
-        <v>0.7436582109479311</v>
+        <v>0.7436582109479306</v>
       </c>
       <c r="F168" s="4" t="n">
         <v>557</v>
       </c>
       <c r="G168" s="3" t="n">
-        <v>0.241655540720961</v>
+        <v>0.2416555407209613</v>
       </c>
       <c r="H168" s="4" t="n">
         <v>181</v>
@@ -8067,19 +8067,19 @@
         </is>
       </c>
       <c r="C169" s="3" t="n">
-        <v>0.0014792899408284</v>
+        <v>0.001479289940828402</v>
       </c>
       <c r="D169" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>0.74112426035503</v>
+        <v>0.7411242603550295</v>
       </c>
       <c r="F169" s="4" t="n">
         <v>501</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>0.24112426035503</v>
+        <v>0.2411242603550296</v>
       </c>
       <c r="H169" s="4" t="n">
         <v>163</v>
@@ -8112,25 +8112,25 @@
         </is>
       </c>
       <c r="C170" s="3" t="n">
-        <v>0.00229885057471264</v>
+        <v>0.002298850574712644</v>
       </c>
       <c r="D170" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>0.71264367816092</v>
+        <v>0.7126436781609196</v>
       </c>
       <c r="F170" s="4" t="n">
         <v>310</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>0.23448275862069</v>
+        <v>0.2344827586206897</v>
       </c>
       <c r="H170" s="4" t="n">
         <v>102</v>
       </c>
       <c r="I170" s="3" t="n">
-        <v>0.0160919540229885</v>
+        <v>0.01609195402298851</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>7</v>
@@ -8157,25 +8157,25 @@
         </is>
       </c>
       <c r="C171" s="3" t="n">
-        <v>0.0145137880986938</v>
+        <v>0.01451378809869376</v>
       </c>
       <c r="D171" s="4" t="n">
         <v>10</v>
       </c>
       <c r="E171" s="3" t="n">
-        <v>0.631349782293179</v>
+        <v>0.6313497822931785</v>
       </c>
       <c r="F171" s="4" t="n">
         <v>435</v>
       </c>
       <c r="G171" s="3" t="n">
-        <v>0.32510885341074</v>
+        <v>0.3251088534107402</v>
       </c>
       <c r="H171" s="4" t="n">
         <v>224</v>
       </c>
       <c r="I171" s="3" t="n">
-        <v>0.00435413642960813</v>
+        <v>0.004354136429608127</v>
       </c>
       <c r="J171" s="4" t="n">
         <v>3</v>
@@ -8202,25 +8202,25 @@
         </is>
       </c>
       <c r="C172" s="3" t="n">
-        <v>0.0017286084701815</v>
+        <v>0.001728608470181504</v>
       </c>
       <c r="D172" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E172" s="3" t="n">
-        <v>0.668107173725151</v>
+        <v>0.6681071737251513</v>
       </c>
       <c r="F172" s="4" t="n">
         <v>773</v>
       </c>
       <c r="G172" s="3" t="n">
-        <v>0.312013828867761</v>
+        <v>0.3120138288677615</v>
       </c>
       <c r="H172" s="4" t="n">
         <v>361</v>
       </c>
       <c r="I172" s="3" t="n">
-        <v>0.00345721694036301</v>
+        <v>0.003457216940363008</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>4</v>
@@ -8247,19 +8247,19 @@
         </is>
       </c>
       <c r="C173" s="3" t="n">
-        <v>0.00793650793650794</v>
+        <v>0.007936507936507936</v>
       </c>
       <c r="D173" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E173" s="3" t="n">
-        <v>0.596371882086168</v>
+        <v>0.5963718820861678</v>
       </c>
       <c r="F173" s="4" t="n">
         <v>526</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>0.380952380952381</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="H173" s="4" t="n">
         <v>336</v>
@@ -8292,25 +8292,25 @@
         </is>
       </c>
       <c r="C174" s="3" t="n">
-        <v>0.00183654729109275</v>
+        <v>0.001836547291092746</v>
       </c>
       <c r="D174" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>0.651974288337925</v>
+        <v>0.6519742883379247</v>
       </c>
       <c r="F174" s="4" t="n">
         <v>710</v>
       </c>
       <c r="G174" s="3" t="n">
-        <v>0.323232323232323</v>
+        <v>0.3232323232323233</v>
       </c>
       <c r="H174" s="4" t="n">
         <v>352</v>
       </c>
       <c r="I174" s="3" t="n">
-        <v>0.000918273645546373</v>
+        <v>0.0009182736455463728</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>1</v>
@@ -8337,25 +8337,25 @@
         </is>
       </c>
       <c r="C175" s="3" t="n">
-        <v>0.0072463768115942</v>
+        <v>0.007246376811594203</v>
       </c>
       <c r="D175" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E175" s="3" t="n">
-        <v>0.628019323671498</v>
+        <v>0.6280193236714976</v>
       </c>
       <c r="F175" s="4" t="n">
         <v>260</v>
       </c>
       <c r="G175" s="3" t="n">
-        <v>0.318840579710145</v>
+        <v>0.3188405797101449</v>
       </c>
       <c r="H175" s="4" t="n">
         <v>132</v>
       </c>
       <c r="I175" s="3" t="n">
-        <v>0.00483091787439613</v>
+        <v>0.004830917874396135</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>2</v>
@@ -8382,13 +8382,13 @@
         </is>
       </c>
       <c r="C176" s="3" t="n">
-        <v>0.00359066427289048</v>
+        <v>0.003590664272890485</v>
       </c>
       <c r="D176" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E176" s="3" t="n">
-        <v>0.6283662477558351</v>
+        <v>0.6283662477558348</v>
       </c>
       <c r="F176" s="4" t="n">
         <v>350</v>
@@ -8400,7 +8400,7 @@
         <v>190</v>
       </c>
       <c r="I176" s="3" t="n">
-        <v>0.00179533213644524</v>
+        <v>0.001795332136445242</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>1</v>
@@ -8427,25 +8427,25 @@
         </is>
       </c>
       <c r="C177" s="3" t="n">
-        <v>0.194277108433735</v>
+        <v>0.1942771084337349</v>
       </c>
       <c r="D177" s="4" t="n">
         <v>129</v>
       </c>
       <c r="E177" s="3" t="n">
-        <v>0.253012048192771</v>
+        <v>0.2530120481927711</v>
       </c>
       <c r="F177" s="4" t="n">
         <v>168</v>
       </c>
       <c r="G177" s="3" t="n">
-        <v>0.5150602409638551</v>
+        <v>0.5150602409638554</v>
       </c>
       <c r="H177" s="4" t="n">
         <v>342</v>
       </c>
       <c r="I177" s="3" t="n">
-        <v>0.0105421686746988</v>
+        <v>0.01054216867469879</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>7</v>
@@ -8472,25 +8472,25 @@
         </is>
       </c>
       <c r="C178" s="3" t="n">
-        <v>0.165064102564103</v>
+        <v>0.1650641025641026</v>
       </c>
       <c r="D178" s="4" t="n">
         <v>103</v>
       </c>
       <c r="E178" s="3" t="n">
-        <v>0.259615384615385</v>
+        <v>0.2596153846153846</v>
       </c>
       <c r="F178" s="4" t="n">
         <v>162</v>
       </c>
       <c r="G178" s="3" t="n">
-        <v>0.544871794871795</v>
+        <v>0.5448717948717948</v>
       </c>
       <c r="H178" s="4" t="n">
         <v>340</v>
       </c>
       <c r="I178" s="3" t="n">
-        <v>0.0128205128205128</v>
+        <v>0.01282051282051282</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>8</v>
@@ -8523,7 +8523,7 @@
         <v>153</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>0.0221354166666667</v>
+        <v>0.02213541666666667</v>
       </c>
       <c r="F179" s="4" t="n">
         <v>17</v>
@@ -8562,25 +8562,25 @@
         </is>
       </c>
       <c r="C180" s="3" t="n">
-        <v>0.354545454545455</v>
+        <v>0.3545454545454546</v>
       </c>
       <c r="D180" s="4" t="n">
         <v>273</v>
       </c>
       <c r="E180" s="3" t="n">
-        <v>0.012987012987013</v>
+        <v>0.01298701298701299</v>
       </c>
       <c r="F180" s="4" t="n">
         <v>10</v>
       </c>
       <c r="G180" s="3" t="n">
-        <v>0.602597402597403</v>
+        <v>0.6025974025974026</v>
       </c>
       <c r="H180" s="4" t="n">
         <v>464</v>
       </c>
       <c r="I180" s="3" t="n">
-        <v>0.00779220779220779</v>
+        <v>0.007792207792207792</v>
       </c>
       <c r="J180" s="4" t="n">
         <v>6</v>
@@ -8613,19 +8613,19 @@
         <v>237</v>
       </c>
       <c r="E181" s="3" t="n">
-        <v>0.00762388818297332</v>
+        <v>0.007623888182973317</v>
       </c>
       <c r="F181" s="4" t="n">
         <v>6</v>
       </c>
       <c r="G181" s="3" t="n">
-        <v>0.675984752223634</v>
+        <v>0.6759847522236341</v>
       </c>
       <c r="H181" s="4" t="n">
         <v>532</v>
       </c>
       <c r="I181" s="3" t="n">
-        <v>0.00254129606099111</v>
+        <v>0.002541296060991106</v>
       </c>
       <c r="J181" s="4" t="n">
         <v>2</v>
@@ -8652,25 +8652,25 @@
         </is>
       </c>
       <c r="C182" s="3" t="n">
-        <v>0.12481644640235</v>
+        <v>0.1248164464023495</v>
       </c>
       <c r="D182" s="4" t="n">
         <v>85</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>0.47870778267254</v>
+        <v>0.4787077826725404</v>
       </c>
       <c r="F182" s="4" t="n">
         <v>326</v>
       </c>
       <c r="G182" s="3" t="n">
-        <v>0.37151248164464</v>
+        <v>0.3715124816446402</v>
       </c>
       <c r="H182" s="4" t="n">
         <v>253</v>
       </c>
       <c r="I182" s="3" t="n">
-        <v>0.00146842878120411</v>
+        <v>0.001468428781204112</v>
       </c>
       <c r="J182" s="4" t="n">
         <v>1</v>
@@ -8697,25 +8697,25 @@
         </is>
       </c>
       <c r="C183" s="3" t="n">
-        <v>0.0418679549114332</v>
+        <v>0.04186795491143317</v>
       </c>
       <c r="D183" s="4" t="n">
         <v>26</v>
       </c>
       <c r="E183" s="3" t="n">
-        <v>0.78743961352657</v>
+        <v>0.7874396135265701</v>
       </c>
       <c r="F183" s="4" t="n">
         <v>489</v>
       </c>
       <c r="G183" s="3" t="n">
-        <v>0.14975845410628</v>
+        <v>0.1497584541062802</v>
       </c>
       <c r="H183" s="4" t="n">
         <v>93</v>
       </c>
       <c r="I183" s="3" t="n">
-        <v>0.00805152979066022</v>
+        <v>0.008051529790660225</v>
       </c>
       <c r="J183" s="4" t="n">
         <v>5</v>
@@ -8742,7 +8742,7 @@
         </is>
       </c>
       <c r="C184" s="3" t="n">
-        <v>0.07568438003220609</v>
+        <v>0.07568438003220612</v>
       </c>
       <c r="D184" s="4" t="n">
         <v>47</v>
@@ -8754,13 +8754,13 @@
         <v>400</v>
       </c>
       <c r="G184" s="3" t="n">
-        <v>0.225442834138486</v>
+        <v>0.2254428341384863</v>
       </c>
       <c r="H184" s="4" t="n">
         <v>140</v>
       </c>
       <c r="I184" s="3" t="n">
-        <v>0.0193236714975845</v>
+        <v>0.01932367149758454</v>
       </c>
       <c r="J184" s="4" t="n">
         <v>12</v>
@@ -8787,13 +8787,13 @@
         </is>
       </c>
       <c r="C185" s="3" t="n">
-        <v>0.0246913580246914</v>
+        <v>0.02469135802469136</v>
       </c>
       <c r="D185" s="4" t="n">
         <v>22</v>
       </c>
       <c r="E185" s="3" t="n">
-        <v>0.753086419753086</v>
+        <v>0.7530864197530864</v>
       </c>
       <c r="F185" s="4" t="n">
         <v>671</v>
@@ -8838,19 +8838,19 @@
         <v>48</v>
       </c>
       <c r="E186" s="3" t="n">
-        <v>0.236928104575163</v>
+        <v>0.2369281045751634</v>
       </c>
       <c r="F186" s="4" t="n">
         <v>145</v>
       </c>
       <c r="G186" s="3" t="n">
-        <v>0.601307189542484</v>
+        <v>0.6013071895424836</v>
       </c>
       <c r="H186" s="4" t="n">
         <v>368</v>
       </c>
       <c r="I186" s="3" t="n">
-        <v>0.0702614379084967</v>
+        <v>0.07026143790849673</v>
       </c>
       <c r="J186" s="4" t="n">
         <v>43</v>
@@ -8877,25 +8877,25 @@
         </is>
       </c>
       <c r="C187" s="3" t="n">
-        <v>0.0474308300395257</v>
+        <v>0.04743083003952569</v>
       </c>
       <c r="D187" s="4" t="n">
         <v>24</v>
       </c>
       <c r="E187" s="3" t="n">
-        <v>0.227272727272727</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="F187" s="4" t="n">
         <v>115</v>
       </c>
       <c r="G187" s="3" t="n">
-        <v>0.612648221343874</v>
+        <v>0.6126482213438735</v>
       </c>
       <c r="H187" s="4" t="n">
         <v>310</v>
       </c>
       <c r="I187" s="3" t="n">
-        <v>0.0909090909090909</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="J187" s="4" t="n">
         <v>46</v>
@@ -8922,7 +8922,7 @@
         </is>
       </c>
       <c r="C188" s="3" t="n">
-        <v>0.220505617977528</v>
+        <v>0.2205056179775281</v>
       </c>
       <c r="D188" s="4" t="n">
         <v>157</v>
@@ -8934,7 +8934,7 @@
         <v>411</v>
       </c>
       <c r="G188" s="3" t="n">
-        <v>0.655898876404494</v>
+        <v>0.6558988764044944</v>
       </c>
       <c r="H188" s="4" t="n">
         <v>467</v>
@@ -8967,25 +8967,25 @@
         </is>
       </c>
       <c r="C189" s="3" t="n">
-        <v>0.0196759259259259</v>
+        <v>0.01967592592592593</v>
       </c>
       <c r="D189" s="4" t="n">
         <v>17</v>
       </c>
       <c r="E189" s="3" t="n">
-        <v>0.831018518518519</v>
+        <v>0.8310185185185185</v>
       </c>
       <c r="F189" s="4" t="n">
         <v>718</v>
       </c>
       <c r="G189" s="3" t="n">
-        <v>0.121527777777778</v>
+        <v>0.1215277777777778</v>
       </c>
       <c r="H189" s="4" t="n">
         <v>105</v>
       </c>
       <c r="I189" s="3" t="n">
-        <v>0.0289351851851852</v>
+        <v>0.02893518518518519</v>
       </c>
       <c r="J189" s="4" t="n">
         <v>25</v>
@@ -9012,19 +9012,19 @@
         </is>
       </c>
       <c r="C190" s="3" t="n">
-        <v>0.07658321060382919</v>
+        <v>0.07658321060382917</v>
       </c>
       <c r="D190" s="4" t="n">
         <v>52</v>
       </c>
       <c r="E190" s="3" t="n">
-        <v>0.70839469808542</v>
+        <v>0.7083946980854198</v>
       </c>
       <c r="F190" s="4" t="n">
         <v>481</v>
       </c>
       <c r="G190" s="3" t="n">
-        <v>0.19440353460972</v>
+        <v>0.1944035346097202</v>
       </c>
       <c r="H190" s="4" t="n">
         <v>132</v>
@@ -9057,25 +9057,25 @@
         </is>
       </c>
       <c r="C191" s="3" t="n">
-        <v>0.0143266475644699</v>
+        <v>0.01432664756446991</v>
       </c>
       <c r="D191" s="4" t="n">
         <v>10</v>
       </c>
       <c r="E191" s="3" t="n">
-        <v>0.865329512893983</v>
+        <v>0.8653295128939829</v>
       </c>
       <c r="F191" s="4" t="n">
         <v>604</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>0.106017191977077</v>
+        <v>0.1060171919770774</v>
       </c>
       <c r="H191" s="4" t="n">
         <v>74</v>
       </c>
       <c r="I191" s="3" t="n">
-        <v>0.00429799426934097</v>
+        <v>0.004297994269340974</v>
       </c>
       <c r="J191" s="4" t="n">
         <v>3</v>
@@ -9102,19 +9102,19 @@
         </is>
       </c>
       <c r="C192" s="3" t="n">
-        <v>0.00683060109289618</v>
+        <v>0.006830601092896175</v>
       </c>
       <c r="D192" s="4" t="n">
         <v>5</v>
       </c>
       <c r="E192" s="3" t="n">
-        <v>0.775956284153005</v>
+        <v>0.7759562841530054</v>
       </c>
       <c r="F192" s="4" t="n">
         <v>568</v>
       </c>
       <c r="G192" s="3" t="n">
-        <v>0.191256830601093</v>
+        <v>0.1912568306010929</v>
       </c>
       <c r="H192" s="4" t="n">
         <v>140</v>
@@ -9147,7 +9147,7 @@
         </is>
       </c>
       <c r="C193" s="3" t="n">
-        <v>0.069204152249135</v>
+        <v>0.06920415224913495</v>
       </c>
       <c r="D193" s="4" t="n">
         <v>40</v>
@@ -9159,7 +9159,7 @@
         <v>107</v>
       </c>
       <c r="G193" s="3" t="n">
-        <v>0.5934256055363319</v>
+        <v>0.5934256055363322</v>
       </c>
       <c r="H193" s="4" t="n">
         <v>343</v>
@@ -9192,25 +9192,25 @@
         </is>
       </c>
       <c r="C194" s="3" t="n">
-        <v>0.08391608391608391</v>
+        <v>0.08391608391608392</v>
       </c>
       <c r="D194" s="4" t="n">
         <v>72</v>
       </c>
       <c r="E194" s="3" t="n">
-        <v>0.269230769230769</v>
+        <v>0.2692307692307692</v>
       </c>
       <c r="F194" s="4" t="n">
         <v>231</v>
       </c>
       <c r="G194" s="3" t="n">
-        <v>0.489510489510489</v>
+        <v>0.4895104895104895</v>
       </c>
       <c r="H194" s="4" t="n">
         <v>420</v>
       </c>
       <c r="I194" s="3" t="n">
-        <v>0.0687645687645688</v>
+        <v>0.06876456876456877</v>
       </c>
       <c r="J194" s="4" t="n">
         <v>59</v>
@@ -9249,13 +9249,13 @@
         <v>20</v>
       </c>
       <c r="G195" s="3" t="n">
-        <v>0.622586872586873</v>
+        <v>0.6225868725868726</v>
       </c>
       <c r="H195" s="4" t="n">
         <v>645</v>
       </c>
       <c r="I195" s="3" t="n">
-        <v>0.00675675675675676</v>
+        <v>0.006756756756756757</v>
       </c>
       <c r="J195" s="4" t="n">
         <v>7</v>
@@ -9282,7 +9282,7 @@
         </is>
       </c>
       <c r="C196" s="3" t="n">
-        <v>0.406518010291595</v>
+        <v>0.4065180102915952</v>
       </c>
       <c r="D196" s="4" t="n">
         <v>237</v>
@@ -9294,13 +9294,13 @@
         <v>8</v>
       </c>
       <c r="G196" s="3" t="n">
-        <v>0.547169811320755</v>
+        <v>0.5471698113207547</v>
       </c>
       <c r="H196" s="4" t="n">
         <v>319</v>
       </c>
       <c r="I196" s="3" t="n">
-        <v>0.008576329331046311</v>
+        <v>0.008576329331046312</v>
       </c>
       <c r="J196" s="4" t="n">
         <v>5</v>
@@ -9327,13 +9327,13 @@
         </is>
       </c>
       <c r="C197" s="3" t="n">
-        <v>0.462857142857143</v>
+        <v>0.4628571428571429</v>
       </c>
       <c r="D197" s="4" t="n">
         <v>324</v>
       </c>
       <c r="E197" s="3" t="n">
-        <v>0.0171428571428571</v>
+        <v>0.01714285714285714</v>
       </c>
       <c r="F197" s="4" t="n">
         <v>12</v>
@@ -9345,7 +9345,7 @@
         <v>350</v>
       </c>
       <c r="I197" s="3" t="n">
-        <v>0.00285714285714286</v>
+        <v>0.002857142857142857</v>
       </c>
       <c r="J197" s="4" t="n">
         <v>2</v>
@@ -9378,13 +9378,13 @@
         <v>288</v>
       </c>
       <c r="E198" s="3" t="n">
-        <v>0.008760951188986231</v>
+        <v>0.008760951188986232</v>
       </c>
       <c r="F198" s="4" t="n">
         <v>7</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>0.588235294117647</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="H198" s="4" t="n">
         <v>470</v>
@@ -9417,13 +9417,13 @@
         </is>
       </c>
       <c r="C199" s="3" t="n">
-        <v>0.0480874316939891</v>
+        <v>0.04808743169398907</v>
       </c>
       <c r="D199" s="4" t="n">
         <v>44</v>
       </c>
       <c r="E199" s="3" t="n">
-        <v>0.622950819672131</v>
+        <v>0.6229508196721312</v>
       </c>
       <c r="F199" s="4" t="n">
         <v>570</v>
@@ -9435,7 +9435,7 @@
         <v>201</v>
       </c>
       <c r="I199" s="3" t="n">
-        <v>0.0218579234972678</v>
+        <v>0.02185792349726776</v>
       </c>
       <c r="J199" s="4" t="n">
         <v>20</v>
@@ -9462,25 +9462,25 @@
         </is>
       </c>
       <c r="C200" s="3" t="n">
-        <v>0.0382571732199787</v>
+        <v>0.03825717321997875</v>
       </c>
       <c r="D200" s="4" t="n">
         <v>36</v>
       </c>
       <c r="E200" s="3" t="n">
-        <v>0.759829968119022</v>
+        <v>0.7598299681190224</v>
       </c>
       <c r="F200" s="4" t="n">
         <v>715</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>0.180658873538789</v>
+        <v>0.1806588735387885</v>
       </c>
       <c r="H200" s="4" t="n">
         <v>170</v>
       </c>
       <c r="I200" s="3" t="n">
-        <v>0.00212539851222104</v>
+        <v>0.002125398512221041</v>
       </c>
       <c r="J200" s="4" t="n">
         <v>2</v>
@@ -9507,25 +9507,25 @@
         </is>
       </c>
       <c r="C201" s="3" t="n">
-        <v>0.0452898550724638</v>
+        <v>0.04528985507246377</v>
       </c>
       <c r="D201" s="4" t="n">
         <v>25</v>
       </c>
       <c r="E201" s="3" t="n">
-        <v>0.615942028985507</v>
+        <v>0.6159420289855072</v>
       </c>
       <c r="F201" s="4" t="n">
         <v>340</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>0.307971014492754</v>
+        <v>0.3079710144927536</v>
       </c>
       <c r="H201" s="4" t="n">
         <v>170</v>
       </c>
       <c r="I201" s="3" t="n">
-        <v>0.00181159420289855</v>
+        <v>0.001811594202898551</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>1</v>
@@ -9552,7 +9552,7 @@
         </is>
       </c>
       <c r="C202" s="3" t="n">
-        <v>0.0118577075098814</v>
+        <v>0.01185770750988142</v>
       </c>
       <c r="D202" s="4" t="n">
         <v>6</v>
@@ -9564,13 +9564,13 @@
         <v>447</v>
       </c>
       <c r="G202" s="3" t="n">
-        <v>0.0790513833992095</v>
+        <v>0.07905138339920949</v>
       </c>
       <c r="H202" s="4" t="n">
         <v>40</v>
       </c>
       <c r="I202" s="3" t="n">
-        <v>0.00592885375494071</v>
+        <v>0.005928853754940711</v>
       </c>
       <c r="J202" s="4" t="n">
         <v>3</v>
@@ -9609,13 +9609,13 @@
         <v>670</v>
       </c>
       <c r="G203" s="3" t="n">
-        <v>0.0763157894736842</v>
+        <v>0.07631578947368421</v>
       </c>
       <c r="H203" s="4" t="n">
         <v>58</v>
       </c>
       <c r="I203" s="3" t="n">
-        <v>0.00526315789473684</v>
+        <v>0.005263157894736842</v>
       </c>
       <c r="J203" s="4" t="n">
         <v>4</v>
@@ -9642,25 +9642,25 @@
         </is>
       </c>
       <c r="C204" s="3" t="n">
-        <v>0.354002254791432</v>
+        <v>0.3540022547914318</v>
       </c>
       <c r="D204" s="4" t="n">
         <v>314</v>
       </c>
       <c r="E204" s="3" t="n">
-        <v>0.0214205186020293</v>
+        <v>0.02142051860202931</v>
       </c>
       <c r="F204" s="4" t="n">
         <v>19</v>
       </c>
       <c r="G204" s="3" t="n">
-        <v>0.574971815107103</v>
+        <v>0.5749718151071026</v>
       </c>
       <c r="H204" s="4" t="n">
         <v>510</v>
       </c>
       <c r="I204" s="3" t="n">
-        <v>0.00676437429537768</v>
+        <v>0.006764374295377677</v>
       </c>
       <c r="J204" s="4" t="n">
         <v>6</v>
@@ -9699,13 +9699,13 @@
         <v>72</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>0.562236286919831</v>
+        <v>0.5622362869198312</v>
       </c>
       <c r="H205" s="4" t="n">
         <v>533</v>
       </c>
       <c r="I205" s="3" t="n">
-        <v>0.0158227848101266</v>
+        <v>0.01582278481012658</v>
       </c>
       <c r="J205" s="4" t="n">
         <v>15</v>
@@ -9732,25 +9732,25 @@
         </is>
       </c>
       <c r="C206" s="3" t="n">
-        <v>0.00171821305841924</v>
+        <v>0.001718213058419244</v>
       </c>
       <c r="D206" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E206" s="3" t="n">
-        <v>0.793814432989691</v>
+        <v>0.7938144329896907</v>
       </c>
       <c r="F206" s="4" t="n">
         <v>462</v>
       </c>
       <c r="G206" s="3" t="n">
-        <v>0.168384879725086</v>
+        <v>0.1683848797250859</v>
       </c>
       <c r="H206" s="4" t="n">
         <v>98</v>
       </c>
       <c r="I206" s="3" t="n">
-        <v>0.00515463917525773</v>
+        <v>0.005154639175257732</v>
       </c>
       <c r="J206" s="4" t="n">
         <v>3</v>
@@ -9777,25 +9777,25 @@
         </is>
       </c>
       <c r="C207" s="3" t="n">
-        <v>0.264150943396226</v>
+        <v>0.2641509433962264</v>
       </c>
       <c r="D207" s="4" t="n">
         <v>336</v>
       </c>
       <c r="E207" s="3" t="n">
-        <v>0.0267295597484277</v>
+        <v>0.02672955974842767</v>
       </c>
       <c r="F207" s="4" t="n">
         <v>34</v>
       </c>
       <c r="G207" s="3" t="n">
-        <v>0.67374213836478</v>
+        <v>0.6737421383647799</v>
       </c>
       <c r="H207" s="4" t="n">
         <v>857</v>
       </c>
       <c r="I207" s="3" t="n">
-        <v>0.00628930817610063</v>
+        <v>0.006289308176100629</v>
       </c>
       <c r="J207" s="4" t="n">
         <v>8</v>
@@ -9822,25 +9822,25 @@
         </is>
       </c>
       <c r="C208" s="3" t="n">
-        <v>0.0109289617486339</v>
+        <v>0.01092896174863388</v>
       </c>
       <c r="D208" s="4" t="n">
         <v>6</v>
       </c>
       <c r="E208" s="3" t="n">
-        <v>0.710382513661202</v>
+        <v>0.7103825136612022</v>
       </c>
       <c r="F208" s="4" t="n">
         <v>390</v>
       </c>
       <c r="G208" s="3" t="n">
-        <v>0.242258652094718</v>
+        <v>0.2422586520947177</v>
       </c>
       <c r="H208" s="4" t="n">
         <v>133</v>
       </c>
       <c r="I208" s="3" t="n">
-        <v>0.00728597449908925</v>
+        <v>0.007285974499089253</v>
       </c>
       <c r="J208" s="4" t="n">
         <v>4</v>
@@ -9867,25 +9867,25 @@
         </is>
       </c>
       <c r="C209" s="3" t="n">
-        <v>0.193602693602694</v>
+        <v>0.1936026936026936</v>
       </c>
       <c r="D209" s="4" t="n">
         <v>115</v>
       </c>
       <c r="E209" s="3" t="n">
-        <v>0.333333333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F209" s="4" t="n">
         <v>198</v>
       </c>
       <c r="G209" s="3" t="n">
-        <v>0.442760942760943</v>
+        <v>0.4427609427609427</v>
       </c>
       <c r="H209" s="4" t="n">
         <v>263</v>
       </c>
       <c r="I209" s="3" t="n">
-        <v>0.00673400673400673</v>
+        <v>0.006734006734006734</v>
       </c>
       <c r="J209" s="4" t="n">
         <v>4</v>
@@ -9912,19 +9912,19 @@
         </is>
       </c>
       <c r="C210" s="3" t="n">
-        <v>0.216129032258064</v>
+        <v>0.2161290322580645</v>
       </c>
       <c r="D210" s="4" t="n">
         <v>201</v>
       </c>
       <c r="E210" s="3" t="n">
-        <v>0.00860215053763441</v>
+        <v>0.008602150537634409</v>
       </c>
       <c r="F210" s="4" t="n">
         <v>8</v>
       </c>
       <c r="G210" s="3" t="n">
-        <v>0.736559139784946</v>
+        <v>0.7365591397849462</v>
       </c>
       <c r="H210" s="4" t="n">
         <v>685</v>
@@ -9957,25 +9957,25 @@
         </is>
       </c>
       <c r="C211" s="3" t="n">
-        <v>0.298181818181818</v>
+        <v>0.2981818181818182</v>
       </c>
       <c r="D211" s="4" t="n">
         <v>164</v>
       </c>
       <c r="E211" s="3" t="n">
-        <v>0.127272727272727</v>
+        <v>0.1272727272727273</v>
       </c>
       <c r="F211" s="4" t="n">
         <v>70</v>
       </c>
       <c r="G211" s="3" t="n">
-        <v>0.512727272727273</v>
+        <v>0.5127272727272727</v>
       </c>
       <c r="H211" s="4" t="n">
         <v>282</v>
       </c>
       <c r="I211" s="3" t="n">
-        <v>0.00727272727272727</v>
+        <v>0.007272727272727273</v>
       </c>
       <c r="J211" s="4" t="n">
         <v>4</v>
@@ -10002,25 +10002,25 @@
         </is>
       </c>
       <c r="C212" s="3" t="n">
-        <v>0.170653907496013</v>
+        <v>0.1706539074960128</v>
       </c>
       <c r="D212" s="4" t="n">
         <v>107</v>
       </c>
       <c r="E212" s="3" t="n">
-        <v>0.00318979266347687</v>
+        <v>0.003189792663476874</v>
       </c>
       <c r="F212" s="4" t="n">
         <v>2</v>
       </c>
       <c r="G212" s="3" t="n">
-        <v>0.669856459330144</v>
+        <v>0.6698564593301436</v>
       </c>
       <c r="H212" s="4" t="n">
         <v>420</v>
       </c>
       <c r="I212" s="3" t="n">
-        <v>0.00956937799043062</v>
+        <v>0.009569377990430622</v>
       </c>
       <c r="J212" s="4" t="n">
         <v>6</v>
@@ -10047,25 +10047,25 @@
         </is>
       </c>
       <c r="C213" s="3" t="n">
-        <v>0.333827893175074</v>
+        <v>0.3338278931750742</v>
       </c>
       <c r="D213" s="4" t="n">
         <v>225</v>
       </c>
       <c r="E213" s="3" t="n">
-        <v>0.0103857566765579</v>
+        <v>0.01038575667655786</v>
       </c>
       <c r="F213" s="4" t="n">
         <v>7</v>
       </c>
       <c r="G213" s="3" t="n">
-        <v>0.594955489614243</v>
+        <v>0.5949554896142433</v>
       </c>
       <c r="H213" s="4" t="n">
         <v>401</v>
       </c>
       <c r="I213" s="3" t="n">
-        <v>0.00593471810089021</v>
+        <v>0.005934718100890208</v>
       </c>
       <c r="J213" s="4" t="n">
         <v>4</v>
@@ -10137,25 +10137,25 @@
         </is>
       </c>
       <c r="C215" s="3" t="n">
-        <v>0.256663376110563</v>
+        <v>0.2566633761105627</v>
       </c>
       <c r="D215" s="4" t="n">
         <v>260</v>
       </c>
       <c r="E215" s="3" t="n">
-        <v>0.0236920039486673</v>
+        <v>0.02369200394866732</v>
       </c>
       <c r="F215" s="4" t="n">
         <v>24</v>
       </c>
       <c r="G215" s="3" t="n">
-        <v>0.600197433366239</v>
+        <v>0.6001974333662389</v>
       </c>
       <c r="H215" s="4" t="n">
         <v>608</v>
       </c>
       <c r="I215" s="3" t="n">
-        <v>0.00394866732477789</v>
+        <v>0.003948667324777887</v>
       </c>
       <c r="J215" s="4" t="n">
         <v>4</v>
@@ -10182,13 +10182,13 @@
         </is>
       </c>
       <c r="C216" s="3" t="n">
-        <v>0.142348754448399</v>
+        <v>0.1423487544483986</v>
       </c>
       <c r="D216" s="4" t="n">
         <v>80</v>
       </c>
       <c r="E216" s="3" t="n">
-        <v>0.124555160142349</v>
+        <v>0.1245551601423488</v>
       </c>
       <c r="F216" s="4" t="n">
         <v>70</v>
@@ -10200,7 +10200,7 @@
         <v>393</v>
       </c>
       <c r="I216" s="3" t="n">
-        <v>0.00533807829181495</v>
+        <v>0.005338078291814947</v>
       </c>
       <c r="J216" s="4" t="n">
         <v>3</v>
@@ -10227,13 +10227,13 @@
         </is>
       </c>
       <c r="C217" s="3" t="n">
-        <v>0.343347639484978</v>
+        <v>0.3433476394849785</v>
       </c>
       <c r="D217" s="4" t="n">
         <v>400</v>
       </c>
       <c r="E217" s="3" t="n">
-        <v>0.0120171673819743</v>
+        <v>0.01201716738197425</v>
       </c>
       <c r="F217" s="4" t="n">
         <v>14</v>
@@ -10245,7 +10245,7 @@
         <v>708</v>
       </c>
       <c r="I217" s="3" t="n">
-        <v>0.00343347639484978</v>
+        <v>0.003433476394849785</v>
       </c>
       <c r="J217" s="4" t="n">
         <v>4</v>
@@ -10272,25 +10272,25 @@
         </is>
       </c>
       <c r="C218" s="3" t="n">
-        <v>0.0229681978798587</v>
+        <v>0.02296819787985866</v>
       </c>
       <c r="D218" s="4" t="n">
         <v>13</v>
       </c>
       <c r="E218" s="3" t="n">
-        <v>0.7067137809187281</v>
+        <v>0.7067137809187279</v>
       </c>
       <c r="F218" s="4" t="n">
         <v>400</v>
       </c>
       <c r="G218" s="3" t="n">
-        <v>0.236749116607774</v>
+        <v>0.2367491166077738</v>
       </c>
       <c r="H218" s="4" t="n">
         <v>134</v>
       </c>
       <c r="I218" s="3" t="n">
-        <v>0.00706713780918728</v>
+        <v>0.007067137809187279</v>
       </c>
       <c r="J218" s="4" t="n">
         <v>4</v>
@@ -10323,19 +10323,19 @@
         <v>107</v>
       </c>
       <c r="E219" s="3" t="n">
-        <v>0.00518134715025907</v>
+        <v>0.005181347150259068</v>
       </c>
       <c r="F219" s="4" t="n">
         <v>4</v>
       </c>
       <c r="G219" s="3" t="n">
-        <v>0.799222797927461</v>
+        <v>0.7992227979274611</v>
       </c>
       <c r="H219" s="4" t="n">
         <v>617</v>
       </c>
       <c r="I219" s="3" t="n">
-        <v>0.0129533678756477</v>
+        <v>0.01295336787564767</v>
       </c>
       <c r="J219" s="4" t="n">
         <v>10</v>
@@ -10362,25 +10362,25 @@
         </is>
       </c>
       <c r="C220" s="3" t="n">
-        <v>0.00263157894736842</v>
+        <v>0.002631578947368421</v>
       </c>
       <c r="D220" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E220" s="3" t="n">
-        <v>0.578947368421053</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="F220" s="4" t="n">
         <v>220</v>
       </c>
       <c r="G220" s="3" t="n">
-        <v>0.384210526315789</v>
+        <v>0.3842105263157894</v>
       </c>
       <c r="H220" s="4" t="n">
         <v>146</v>
       </c>
       <c r="I220" s="3" t="n">
-        <v>0.00263157894736842</v>
+        <v>0.002631578947368421</v>
       </c>
       <c r="J220" s="4" t="n">
         <v>1</v>
@@ -10407,25 +10407,25 @@
         </is>
       </c>
       <c r="C221" s="3" t="n">
-        <v>0.205235602094241</v>
+        <v>0.2052356020942408</v>
       </c>
       <c r="D221" s="4" t="n">
         <v>196</v>
       </c>
       <c r="E221" s="3" t="n">
-        <v>0.0115183246073298</v>
+        <v>0.01151832460732984</v>
       </c>
       <c r="F221" s="4" t="n">
         <v>11</v>
       </c>
       <c r="G221" s="3" t="n">
-        <v>0.783246073298429</v>
+        <v>0.7832460732984293</v>
       </c>
       <c r="H221" s="4" t="n">
         <v>748</v>
       </c>
       <c r="I221" s="3" t="n">
-        <v>0.00104712041884817</v>
+        <v>0.001047120418848168</v>
       </c>
       <c r="J221" s="4" t="n">
         <v>1</v>
@@ -10458,13 +10458,13 @@
         <v>0</v>
       </c>
       <c r="E222" s="3" t="n">
-        <v>0.840749414519906</v>
+        <v>0.8407494145199064</v>
       </c>
       <c r="F222" s="4" t="n">
         <v>718</v>
       </c>
       <c r="G222" s="3" t="n">
-        <v>0.131147540983607</v>
+        <v>0.1311475409836066</v>
       </c>
       <c r="H222" s="4" t="n">
         <v>112</v>
@@ -10497,19 +10497,19 @@
         </is>
       </c>
       <c r="C223" s="3" t="n">
-        <v>0.040920716112532</v>
+        <v>0.04092071611253197</v>
       </c>
       <c r="D223" s="4" t="n">
         <v>32</v>
       </c>
       <c r="E223" s="3" t="n">
-        <v>0.531969309462916</v>
+        <v>0.5319693094629157</v>
       </c>
       <c r="F223" s="4" t="n">
         <v>416</v>
       </c>
       <c r="G223" s="3" t="n">
-        <v>0.41304347826087</v>
+        <v>0.4130434782608696</v>
       </c>
       <c r="H223" s="4" t="n">
         <v>323</v>
@@ -10542,19 +10542,19 @@
         </is>
       </c>
       <c r="C224" s="3" t="n">
-        <v>0.0173333333333333</v>
+        <v>0.01733333333333333</v>
       </c>
       <c r="D224" s="4" t="n">
         <v>13</v>
       </c>
       <c r="E224" s="3" t="n">
-        <v>0.0109866666666667</v>
+        <v>0.01098666666666667</v>
       </c>
       <c r="F224" s="4" t="n">
         <v>8</v>
       </c>
       <c r="G224" s="3" t="n">
-        <v>0.133333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="H224" s="4" t="n">
         <v>100</v>
@@ -10587,19 +10587,19 @@
         </is>
       </c>
       <c r="C225" s="3" t="n">
-        <v>0.123022847100176</v>
+        <v>0.1230228471001757</v>
       </c>
       <c r="D225" s="4" t="n">
         <v>140</v>
       </c>
       <c r="E225" s="3" t="n">
-        <v>0.5597539543058</v>
+        <v>0.5597539543057997</v>
       </c>
       <c r="F225" s="4" t="n">
         <v>637</v>
       </c>
       <c r="G225" s="3" t="n">
-        <v>0.289982425307557</v>
+        <v>0.2899824253075571</v>
       </c>
       <c r="H225" s="4" t="n">
         <v>330</v>
@@ -10632,25 +10632,25 @@
         </is>
       </c>
       <c r="C226" s="3" t="n">
-        <v>0.161061946902655</v>
+        <v>0.1610619469026549</v>
       </c>
       <c r="D226" s="4" t="n">
         <v>91</v>
       </c>
       <c r="E226" s="3" t="n">
-        <v>0.357522123893805</v>
+        <v>0.3575221238938053</v>
       </c>
       <c r="F226" s="4" t="n">
         <v>202</v>
       </c>
       <c r="G226" s="3" t="n">
-        <v>0.43716814159292</v>
+        <v>0.4371681415929203</v>
       </c>
       <c r="H226" s="4" t="n">
         <v>247</v>
       </c>
       <c r="I226" s="3" t="n">
-        <v>0.00707964601769911</v>
+        <v>0.007079646017699115</v>
       </c>
       <c r="J226" s="4" t="n">
         <v>4</v>
@@ -10677,25 +10677,25 @@
         </is>
       </c>
       <c r="C227" s="3" t="n">
-        <v>0.346049046321526</v>
+        <v>0.3460490463215259</v>
       </c>
       <c r="D227" s="4" t="n">
         <v>381</v>
       </c>
       <c r="E227" s="3" t="n">
-        <v>0.00544959128065395</v>
+        <v>0.005449591280653951</v>
       </c>
       <c r="F227" s="4" t="n">
         <v>6</v>
       </c>
       <c r="G227" s="3" t="n">
-        <v>0.556766575840145</v>
+        <v>0.5567665758401453</v>
       </c>
       <c r="H227" s="4" t="n">
         <v>613</v>
       </c>
       <c r="I227" s="3" t="n">
-        <v>0.00454132606721163</v>
+        <v>0.004541326067211626</v>
       </c>
       <c r="J227" s="4" t="n">
         <v>5</v>
@@ -10728,19 +10728,19 @@
         <v>2</v>
       </c>
       <c r="E228" s="3" t="n">
-        <v>0.79304897314376</v>
+        <v>0.7930489731437599</v>
       </c>
       <c r="F228" s="4" t="n">
         <v>502</v>
       </c>
       <c r="G228" s="3" t="n">
-        <v>0.200631911532385</v>
+        <v>0.2006319115323855</v>
       </c>
       <c r="H228" s="4" t="n">
         <v>127</v>
       </c>
       <c r="I228" s="3" t="n">
-        <v>0.00157977883096367</v>
+        <v>0.001579778830963665</v>
       </c>
       <c r="J228" s="4" t="n">
         <v>1</v>
@@ -10767,25 +10767,25 @@
         </is>
       </c>
       <c r="C229" s="3" t="n">
-        <v>0.046551724137931</v>
+        <v>0.04655172413793104</v>
       </c>
       <c r="D229" s="4" t="n">
         <v>27</v>
       </c>
       <c r="E229" s="3" t="n">
-        <v>0.625862068965517</v>
+        <v>0.6258620689655172</v>
       </c>
       <c r="F229" s="4" t="n">
         <v>363</v>
       </c>
       <c r="G229" s="3" t="n">
-        <v>0.313793103448276</v>
+        <v>0.3137931034482759</v>
       </c>
       <c r="H229" s="4" t="n">
         <v>182</v>
       </c>
       <c r="I229" s="3" t="n">
-        <v>0.00344827586206896</v>
+        <v>0.003448275862068965</v>
       </c>
       <c r="J229" s="4" t="n">
         <v>2</v>
@@ -10812,19 +10812,19 @@
         </is>
       </c>
       <c r="C230" s="3" t="n">
-        <v>0.19054441260745</v>
+        <v>0.1905444126074499</v>
       </c>
       <c r="D230" s="4" t="n">
         <v>133</v>
       </c>
       <c r="E230" s="3" t="n">
-        <v>0.181948424068768</v>
+        <v>0.1819484240687679</v>
       </c>
       <c r="F230" s="4" t="n">
         <v>127</v>
       </c>
       <c r="G230" s="3" t="n">
-        <v>0.573065902578797</v>
+        <v>0.5730659025787965</v>
       </c>
       <c r="H230" s="4" t="n">
         <v>400</v>
@@ -10863,19 +10863,19 @@
         <v>0</v>
       </c>
       <c r="E231" s="3" t="n">
-        <v>0.494464944649446</v>
+        <v>0.4944649446494465</v>
       </c>
       <c r="F231" s="4" t="n">
         <v>402</v>
       </c>
       <c r="G231" s="3" t="n">
-        <v>0.40590405904059</v>
+        <v>0.4059040590405904</v>
       </c>
       <c r="H231" s="4" t="n">
         <v>330</v>
       </c>
       <c r="I231" s="3" t="n">
-        <v>0.00492004920049201</v>
+        <v>0.004920049200492005</v>
       </c>
       <c r="J231" s="4" t="n">
         <v>4</v>
@@ -10902,7 +10902,7 @@
         </is>
       </c>
       <c r="C232" s="3" t="n">
-        <v>0.116216216216216</v>
+        <v>0.1162162162162162</v>
       </c>
       <c r="D232" s="4" t="n">
         <v>43</v>
@@ -10914,13 +10914,13 @@
         <v>0</v>
       </c>
       <c r="G232" s="3" t="n">
-        <v>0.848648648648649</v>
+        <v>0.8486486486486486</v>
       </c>
       <c r="H232" s="4" t="n">
         <v>314</v>
       </c>
       <c r="I232" s="3" t="n">
-        <v>0.00810810810810811</v>
+        <v>0.008108108108108109</v>
       </c>
       <c r="J232" s="4" t="n">
         <v>3</v>
@@ -10953,19 +10953,19 @@
         <v>0</v>
       </c>
       <c r="E233" s="3" t="n">
-        <v>0.749596122778675</v>
+        <v>0.7495961227786753</v>
       </c>
       <c r="F233" s="4" t="n">
         <v>464</v>
       </c>
       <c r="G233" s="3" t="n">
-        <v>0.21486268174475</v>
+        <v>0.2148626817447496</v>
       </c>
       <c r="H233" s="4" t="n">
         <v>133</v>
       </c>
       <c r="I233" s="3" t="n">
-        <v>0.00646203554119548</v>
+        <v>0.006462035541195477</v>
       </c>
       <c r="J233" s="4" t="n">
         <v>4</v>
@@ -10992,25 +10992,25 @@
         </is>
       </c>
       <c r="C234" s="3" t="n">
-        <v>0.00627240143369176</v>
+        <v>0.006272401433691756</v>
       </c>
       <c r="D234" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E234" s="3" t="n">
-        <v>0.5483870967741939</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="F234" s="4" t="n">
         <v>612</v>
       </c>
       <c r="G234" s="3" t="n">
-        <v>0.379928315412186</v>
+        <v>0.3799283154121864</v>
       </c>
       <c r="H234" s="4" t="n">
         <v>424</v>
       </c>
       <c r="I234" s="3" t="n">
-        <v>0.00268817204301075</v>
+        <v>0.002688172043010753</v>
       </c>
       <c r="J234" s="4" t="n">
         <v>3</v>
@@ -11037,25 +11037,25 @@
         </is>
       </c>
       <c r="C235" s="3" t="n">
-        <v>0.0897009966777409</v>
+        <v>0.08970099667774087</v>
       </c>
       <c r="D235" s="4" t="n">
         <v>54</v>
       </c>
       <c r="E235" s="3" t="n">
-        <v>0.318936877076412</v>
+        <v>0.3189368770764119</v>
       </c>
       <c r="F235" s="4" t="n">
         <v>192</v>
       </c>
       <c r="G235" s="3" t="n">
-        <v>0.561461794019934</v>
+        <v>0.5614617940199336</v>
       </c>
       <c r="H235" s="4" t="n">
         <v>338</v>
       </c>
       <c r="I235" s="3" t="n">
-        <v>0.0116279069767442</v>
+        <v>0.01162790697674419</v>
       </c>
       <c r="J235" s="4" t="n">
         <v>7</v>
@@ -11088,19 +11088,19 @@
         <v>21</v>
       </c>
       <c r="E236" s="3" t="n">
-        <v>0.256214149139579</v>
+        <v>0.2562141491395794</v>
       </c>
       <c r="F236" s="4" t="n">
         <v>134</v>
       </c>
       <c r="G236" s="3" t="n">
-        <v>0.674952198852772</v>
+        <v>0.6749521988527725</v>
       </c>
       <c r="H236" s="4" t="n">
         <v>353</v>
       </c>
       <c r="I236" s="3" t="n">
-        <v>0.00573613766730402</v>
+        <v>0.005736137667304016</v>
       </c>
       <c r="J236" s="4" t="n">
         <v>3</v>
@@ -11127,25 +11127,25 @@
         </is>
       </c>
       <c r="C237" s="3" t="n">
-        <v>0.00253164556962025</v>
+        <v>0.002531645569620253</v>
       </c>
       <c r="D237" s="4" t="n">
         <v>1</v>
       </c>
       <c r="E237" s="3" t="n">
-        <v>0.70379746835443</v>
+        <v>0.7037974683544304</v>
       </c>
       <c r="F237" s="4" t="n">
         <v>278</v>
       </c>
       <c r="G237" s="3" t="n">
-        <v>0.253164556962025</v>
+        <v>0.2531645569620253</v>
       </c>
       <c r="H237" s="4" t="n">
         <v>100</v>
       </c>
       <c r="I237" s="3" t="n">
-        <v>0.00759493670886076</v>
+        <v>0.007594936708860759</v>
       </c>
       <c r="J237" s="4" t="n">
         <v>3</v>
@@ -11172,25 +11172,25 @@
         </is>
       </c>
       <c r="C238" s="3" t="n">
-        <v>0.00364298724954463</v>
+        <v>0.003642987249544627</v>
       </c>
       <c r="D238" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E238" s="3" t="n">
-        <v>0.861566484517304</v>
+        <v>0.8615664845173042</v>
       </c>
       <c r="F238" s="4" t="n">
         <v>473</v>
       </c>
       <c r="G238" s="3" t="n">
-        <v>0.120218579234973</v>
+        <v>0.1202185792349727</v>
       </c>
       <c r="H238" s="4" t="n">
         <v>66</v>
       </c>
       <c r="I238" s="3" t="n">
-        <v>0.00182149362477231</v>
+        <v>0.001821493624772313</v>
       </c>
       <c r="J238" s="4" t="n">
         <v>1</v>
@@ -11217,19 +11217,19 @@
         </is>
       </c>
       <c r="C239" s="3" t="n">
-        <v>0.0497512437810945</v>
+        <v>0.04975124378109453</v>
       </c>
       <c r="D239" s="4" t="n">
         <v>40</v>
       </c>
       <c r="E239" s="3" t="n">
-        <v>0.253731343283582</v>
+        <v>0.2537313432835821</v>
       </c>
       <c r="F239" s="4" t="n">
         <v>204</v>
       </c>
       <c r="G239" s="3" t="n">
-        <v>0.610696517412935</v>
+        <v>0.6106965174129353</v>
       </c>
       <c r="H239" s="4" t="n">
         <v>491</v>
@@ -11262,25 +11262,25 @@
         </is>
       </c>
       <c r="C240" s="3" t="n">
-        <v>0.0482866043613707</v>
+        <v>0.04828660436137071</v>
       </c>
       <c r="D240" s="4" t="n">
         <v>31</v>
       </c>
       <c r="E240" s="3" t="n">
-        <v>0.520249221183801</v>
+        <v>0.5202492211838006</v>
       </c>
       <c r="F240" s="4" t="n">
         <v>334</v>
       </c>
       <c r="G240" s="3" t="n">
-        <v>0.400311526479751</v>
+        <v>0.4003115264797508</v>
       </c>
       <c r="H240" s="4" t="n">
         <v>257</v>
       </c>
       <c r="I240" s="3" t="n">
-        <v>0.00623052959501558</v>
+        <v>0.006230529595015576</v>
       </c>
       <c r="J240" s="4" t="n">
         <v>4</v>
@@ -11307,25 +11307,25 @@
         </is>
       </c>
       <c r="C241" s="3" t="n">
-        <v>0.0503685503685504</v>
+        <v>0.05036855036855037</v>
       </c>
       <c r="D241" s="4" t="n">
         <v>41</v>
       </c>
       <c r="E241" s="3" t="n">
-        <v>0.401719901719902</v>
+        <v>0.4017199017199017</v>
       </c>
       <c r="F241" s="4" t="n">
         <v>327</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>0.528255528255528</v>
+        <v>0.5282555282555282</v>
       </c>
       <c r="H241" s="4" t="n">
         <v>430</v>
       </c>
       <c r="I241" s="3" t="n">
-        <v>0.00245700245700246</v>
+        <v>0.002457002457002457</v>
       </c>
       <c r="J241" s="4" t="n">
         <v>2</v>
@@ -11352,13 +11352,13 @@
         </is>
       </c>
       <c r="C242" s="3" t="n">
-        <v>0.0207900207900208</v>
+        <v>0.02079002079002079</v>
       </c>
       <c r="D242" s="4" t="n">
         <v>20</v>
       </c>
       <c r="E242" s="3" t="n">
-        <v>0.767151767151767</v>
+        <v>0.7671517671517671</v>
       </c>
       <c r="F242" s="4" t="n">
         <v>738</v>
@@ -11370,7 +11370,7 @@
         <v>178</v>
       </c>
       <c r="I242" s="3" t="n">
-        <v>0.00415800415800416</v>
+        <v>0.004158004158004158</v>
       </c>
       <c r="J242" s="4" t="n">
         <v>4</v>
@@ -11397,25 +11397,25 @@
         </is>
       </c>
       <c r="C243" s="3" t="n">
-        <v>0.00594353640416048</v>
+        <v>0.005943536404160475</v>
       </c>
       <c r="D243" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E243" s="3" t="n">
-        <v>0.683506686478455</v>
+        <v>0.6835066864784547</v>
       </c>
       <c r="F243" s="4" t="n">
         <v>460</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>0.282317979197623</v>
+        <v>0.2823179791976226</v>
       </c>
       <c r="H243" s="4" t="n">
         <v>190</v>
       </c>
       <c r="I243" s="3" t="n">
-        <v>0.00742942050520059</v>
+        <v>0.007429420505200594</v>
       </c>
       <c r="J243" s="4" t="n">
         <v>5</v>
@@ -11448,19 +11448,19 @@
         <v>0</v>
       </c>
       <c r="E244" s="3" t="n">
-        <v>0.735135135135135</v>
+        <v>0.7351351351351352</v>
       </c>
       <c r="F244" s="4" t="n">
         <v>544</v>
       </c>
       <c r="G244" s="3" t="n">
-        <v>0.252702702702703</v>
+        <v>0.2527027027027027</v>
       </c>
       <c r="H244" s="4" t="n">
         <v>187</v>
       </c>
       <c r="I244" s="3" t="n">
-        <v>0.00135135135135135</v>
+        <v>0.001351351351351351</v>
       </c>
       <c r="J244" s="4" t="n">
         <v>1</v>
@@ -11487,25 +11487,25 @@
         </is>
       </c>
       <c r="C245" s="3" t="n">
-        <v>0.0110987791342952</v>
+        <v>0.01109877913429523</v>
       </c>
       <c r="D245" s="4" t="n">
         <v>10</v>
       </c>
       <c r="E245" s="3" t="n">
-        <v>0.554938956714761</v>
+        <v>0.5549389567147613</v>
       </c>
       <c r="F245" s="4" t="n">
         <v>500</v>
       </c>
       <c r="G245" s="3" t="n">
-        <v>0.468368479467259</v>
+        <v>0.4683684794672586</v>
       </c>
       <c r="H245" s="4" t="n">
         <v>422</v>
       </c>
       <c r="I245" s="3" t="n">
-        <v>0.00332963374028857</v>
+        <v>0.003329633740288568</v>
       </c>
       <c r="J245" s="4" t="n">
         <v>3</v>
@@ -11538,7 +11538,7 @@
         <v>0</v>
       </c>
       <c r="E246" s="3" t="n">
-        <v>0.495426829268293</v>
+        <v>0.4954268292682927</v>
       </c>
       <c r="F246" s="4" t="n">
         <v>325</v>
@@ -11550,7 +11550,7 @@
         <v>312</v>
       </c>
       <c r="I246" s="3" t="n">
-        <v>0.00457317073170732</v>
+        <v>0.004573170731707317</v>
       </c>
       <c r="J246" s="4" t="n">
         <v>3</v>
@@ -11577,13 +11577,13 @@
         </is>
       </c>
       <c r="C247" s="3" t="n">
-        <v>0.0188323917137476</v>
+        <v>0.01883239171374764</v>
       </c>
       <c r="D247" s="4" t="n">
         <v>20</v>
       </c>
       <c r="E247" s="3" t="n">
-        <v>0.602636534839925</v>
+        <v>0.6026365348399246</v>
       </c>
       <c r="F247" s="4" t="n">
         <v>640</v>
@@ -11622,25 +11622,25 @@
         </is>
       </c>
       <c r="C248" s="3" t="n">
-        <v>0.046029919447641</v>
+        <v>0.04602991944764097</v>
       </c>
       <c r="D248" s="4" t="n">
         <v>40</v>
       </c>
       <c r="E248" s="3" t="n">
-        <v>0.498273878020714</v>
+        <v>0.4982738780207135</v>
       </c>
       <c r="F248" s="4" t="n">
         <v>433</v>
       </c>
       <c r="G248" s="3" t="n">
-        <v>0.437284234752589</v>
+        <v>0.4372842347525892</v>
       </c>
       <c r="H248" s="4" t="n">
         <v>380</v>
       </c>
       <c r="I248" s="3" t="n">
-        <v>0.00115074798619102</v>
+        <v>0.001150747986191024</v>
       </c>
       <c r="J248" s="4" t="n">
         <v>1</v>
@@ -11667,25 +11667,25 @@
         </is>
       </c>
       <c r="C249" s="3" t="n">
-        <v>0.0434782608695652</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="D249" s="4" t="n">
         <v>20</v>
       </c>
       <c r="E249" s="3" t="n">
-        <v>0.660869565217391</v>
+        <v>0.6608695652173913</v>
       </c>
       <c r="F249" s="4" t="n">
         <v>304</v>
       </c>
       <c r="G249" s="3" t="n">
-        <v>0.256521739130435</v>
+        <v>0.2565217391304348</v>
       </c>
       <c r="H249" s="4" t="n">
         <v>118</v>
       </c>
       <c r="I249" s="3" t="n">
-        <v>0.00869565217391304</v>
+        <v>0.008695652173913044</v>
       </c>
       <c r="J249" s="4" t="n">
         <v>4</v>
@@ -11724,7 +11724,7 @@
         <v>365</v>
       </c>
       <c r="G250" s="3" t="n">
-        <v>0.420738974970203</v>
+        <v>0.4207389749702026</v>
       </c>
       <c r="H250" s="4" t="n">
         <v>353</v>
@@ -11763,19 +11763,19 @@
         <v>0</v>
       </c>
       <c r="E251" s="3" t="n">
-        <v>0.6645408163265309</v>
+        <v>0.6645408163265306</v>
       </c>
       <c r="F251" s="4" t="n">
         <v>521</v>
       </c>
       <c r="G251" s="3" t="n">
-        <v>0.272959183673469</v>
+        <v>0.2729591836734694</v>
       </c>
       <c r="H251" s="4" t="n">
         <v>214</v>
       </c>
       <c r="I251" s="3" t="n">
-        <v>0.0038265306122449</v>
+        <v>0.003826530612244898</v>
       </c>
       <c r="J251" s="4" t="n">
         <v>3</v>
@@ -11808,19 +11808,19 @@
         <v>0</v>
       </c>
       <c r="E252" s="3" t="n">
-        <v>0.612579762989973</v>
+        <v>0.6125797629899726</v>
       </c>
       <c r="F252" s="4" t="n">
         <v>672</v>
       </c>
       <c r="G252" s="3" t="n">
-        <v>0.363719234275296</v>
+        <v>0.3637192342752963</v>
       </c>
       <c r="H252" s="4" t="n">
         <v>399</v>
       </c>
       <c r="I252" s="3" t="n">
-        <v>0.00364630811303555</v>
+        <v>0.003646308113035551</v>
       </c>
       <c r="J252" s="4" t="n">
         <v>4</v>
@@ -11853,13 +11853,13 @@
         <v>0</v>
       </c>
       <c r="E253" s="3" t="n">
-        <v>0.555096418732782</v>
+        <v>0.5550964187327824</v>
       </c>
       <c r="F253" s="4" t="n">
         <v>403</v>
       </c>
       <c r="G253" s="3" t="n">
-        <v>0.424242424242424</v>
+        <v>0.4242424242424243</v>
       </c>
       <c r="H253" s="4" t="n">
         <v>308</v>
@@ -11892,25 +11892,25 @@
         </is>
       </c>
       <c r="C254" s="3" t="n">
-        <v>0.0221465076660988</v>
+        <v>0.02214650766609881</v>
       </c>
       <c r="D254" s="4" t="n">
         <v>13</v>
       </c>
       <c r="E254" s="3" t="n">
-        <v>0.5672913117546849</v>
+        <v>0.5672913117546848</v>
       </c>
       <c r="F254" s="4" t="n">
         <v>333</v>
       </c>
       <c r="G254" s="3" t="n">
-        <v>0.374787052810903</v>
+        <v>0.3747870528109029</v>
       </c>
       <c r="H254" s="4" t="n">
         <v>220</v>
       </c>
       <c r="I254" s="3" t="n">
-        <v>0.00681431005110732</v>
+        <v>0.006814310051107325</v>
       </c>
       <c r="J254" s="4" t="n">
         <v>4</v>
@@ -11937,19 +11937,19 @@
         </is>
       </c>
       <c r="C255" s="3" t="n">
-        <v>0.0127504553734062</v>
+        <v>0.01275045537340619</v>
       </c>
       <c r="D255" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E255" s="3" t="n">
-        <v>0.693989071038251</v>
+        <v>0.6939890710382514</v>
       </c>
       <c r="F255" s="4" t="n">
         <v>381</v>
       </c>
       <c r="G255" s="3" t="n">
-        <v>0.265938069216758</v>
+        <v>0.2659380692167577</v>
       </c>
       <c r="H255" s="4" t="n">
         <v>146</v>
@@ -11982,19 +11982,19 @@
         </is>
       </c>
       <c r="C256" s="3" t="n">
-        <v>0.0150684931506849</v>
+        <v>0.01506849315068493</v>
       </c>
       <c r="D256" s="4" t="n">
         <v>11</v>
       </c>
       <c r="E256" s="3" t="n">
-        <v>0.668493150684932</v>
+        <v>0.6684931506849315</v>
       </c>
       <c r="F256" s="4" t="n">
         <v>488</v>
       </c>
       <c r="G256" s="3" t="n">
-        <v>0.294520547945205</v>
+        <v>0.2945205479452055</v>
       </c>
       <c r="H256" s="4" t="n">
         <v>215</v>
@@ -12027,19 +12027,19 @@
         </is>
       </c>
       <c r="C257" s="3" t="n">
-        <v>0.008739076154806491</v>
+        <v>0.008739076154806492</v>
       </c>
       <c r="D257" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E257" s="3" t="n">
-        <v>0.6916354556804</v>
+        <v>0.6916354556803995</v>
       </c>
       <c r="F257" s="4" t="n">
         <v>554</v>
       </c>
       <c r="G257" s="3" t="n">
-        <v>0.269662921348315</v>
+        <v>0.2696629213483146</v>
       </c>
       <c r="H257" s="4" t="n">
         <v>216</v>
@@ -12084,7 +12084,7 @@
         <v>335</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>0.327619047619048</v>
+        <v>0.3276190476190476</v>
       </c>
       <c r="H258" s="4" t="n">
         <v>172</v>
@@ -12117,25 +12117,25 @@
         </is>
       </c>
       <c r="C259" s="3" t="n">
-        <v>0.00452488687782805</v>
+        <v>0.004524886877828055</v>
       </c>
       <c r="D259" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E259" s="3" t="n">
-        <v>0.735294117647059</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="F259" s="4" t="n">
         <v>650</v>
       </c>
       <c r="G259" s="3" t="n">
-        <v>0.23868778280543</v>
+        <v>0.2386877828054299</v>
       </c>
       <c r="H259" s="4" t="n">
         <v>211</v>
       </c>
       <c r="I259" s="3" t="n">
-        <v>0.00339366515837104</v>
+        <v>0.003393665158371041</v>
       </c>
       <c r="J259" s="4" t="n">
         <v>3</v>
@@ -12162,19 +12162,19 @@
         </is>
       </c>
       <c r="C260" s="3" t="n">
-        <v>0.0073394495412844</v>
+        <v>0.007339449541284404</v>
       </c>
       <c r="D260" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E260" s="3" t="n">
-        <v>0.587155963302752</v>
+        <v>0.5871559633027523</v>
       </c>
       <c r="F260" s="4" t="n">
         <v>320</v>
       </c>
       <c r="G260" s="3" t="n">
-        <v>0.330275229357798</v>
+        <v>0.3302752293577982</v>
       </c>
       <c r="H260" s="4" t="n">
         <v>180</v>
@@ -12207,25 +12207,25 @@
         </is>
       </c>
       <c r="C261" s="3" t="n">
-        <v>0.00690846286701209</v>
+        <v>0.006908462867012089</v>
       </c>
       <c r="D261" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E261" s="3" t="n">
-        <v>0.6286701208981</v>
+        <v>0.6286701208981001</v>
       </c>
       <c r="F261" s="4" t="n">
         <v>364</v>
       </c>
       <c r="G261" s="3" t="n">
-        <v>0.33160621761658</v>
+        <v>0.3316062176165803</v>
       </c>
       <c r="H261" s="4" t="n">
         <v>192</v>
       </c>
       <c r="I261" s="3" t="n">
-        <v>0.00345423143350604</v>
+        <v>0.003454231433506045</v>
       </c>
       <c r="J261" s="4" t="n">
         <v>2</v>
@@ -12252,19 +12252,19 @@
         </is>
       </c>
       <c r="C262" s="3" t="n">
-        <v>0.00652173913043478</v>
+        <v>0.006521739130434782</v>
       </c>
       <c r="D262" s="4" t="n">
         <v>6</v>
       </c>
       <c r="E262" s="3" t="n">
-        <v>0.759782608695652</v>
+        <v>0.7597826086956522</v>
       </c>
       <c r="F262" s="4" t="n">
         <v>699</v>
       </c>
       <c r="G262" s="3" t="n">
-        <v>0.209782608695652</v>
+        <v>0.2097826086956522</v>
       </c>
       <c r="H262" s="4" t="n">
         <v>193</v>
@@ -12297,13 +12297,13 @@
         </is>
       </c>
       <c r="C263" s="3" t="n">
-        <v>0.417227456258412</v>
+        <v>0.4172274562584118</v>
       </c>
       <c r="D263" s="4" t="n">
         <v>310</v>
       </c>
       <c r="E263" s="3" t="n">
-        <v>0.0605652759084791</v>
+        <v>0.06056527590847914</v>
       </c>
       <c r="F263" s="4" t="n">
         <v>45</v>
@@ -12315,7 +12315,7 @@
         <v>362</v>
       </c>
       <c r="I263" s="3" t="n">
-        <v>0.009421265141318981</v>
+        <v>0.009421265141318977</v>
       </c>
       <c r="J263" s="4" t="n">
         <v>7</v>
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="C264" s="3" t="n">
-        <v>0.26969696969697</v>
+        <v>0.2696969696969697</v>
       </c>
       <c r="D264" s="4" t="n">
         <v>267</v>
@@ -12354,13 +12354,13 @@
         <v>4</v>
       </c>
       <c r="G264" s="3" t="n">
-        <v>0.666666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H264" s="4" t="n">
         <v>660</v>
       </c>
       <c r="I264" s="3" t="n">
-        <v>0.0111111111111111</v>
+        <v>0.01111111111111111</v>
       </c>
       <c r="J264" s="4" t="n">
         <v>11</v>
@@ -12387,25 +12387,25 @@
         </is>
       </c>
       <c r="C265" s="3" t="n">
-        <v>0.010590015128593</v>
+        <v>0.01059001512859304</v>
       </c>
       <c r="D265" s="4" t="n">
         <v>7</v>
       </c>
       <c r="E265" s="3" t="n">
-        <v>0.396369137670197</v>
+        <v>0.3963691376701967</v>
       </c>
       <c r="F265" s="4" t="n">
         <v>262</v>
       </c>
       <c r="G265" s="3" t="n">
-        <v>0.544629349470499</v>
+        <v>0.5446293494704992</v>
       </c>
       <c r="H265" s="4" t="n">
         <v>360</v>
       </c>
       <c r="I265" s="3" t="n">
-        <v>0.00605143721633888</v>
+        <v>0.006051437216338881</v>
       </c>
       <c r="J265" s="4" t="n">
         <v>4</v>
@@ -12432,25 +12432,25 @@
         </is>
       </c>
       <c r="C266" s="3" t="n">
-        <v>0.308588064046579</v>
+        <v>0.3085880640465793</v>
       </c>
       <c r="D266" s="4" t="n">
         <v>212</v>
       </c>
       <c r="E266" s="3" t="n">
-        <v>0.008733624454148469</v>
+        <v>0.008733624454148471</v>
       </c>
       <c r="F266" s="4" t="n">
         <v>6</v>
       </c>
       <c r="G266" s="3" t="n">
-        <v>0.640465793304221</v>
+        <v>0.6404657933042213</v>
       </c>
       <c r="H266" s="4" t="n">
         <v>440</v>
       </c>
       <c r="I266" s="3" t="n">
-        <v>0.00582241630276565</v>
+        <v>0.005822416302765648</v>
       </c>
       <c r="J266" s="4" t="n">
         <v>4</v>
@@ -12477,19 +12477,19 @@
         </is>
       </c>
       <c r="C267" s="3" t="n">
-        <v>0.256081946222791</v>
+        <v>0.2560819462227913</v>
       </c>
       <c r="D267" s="4" t="n">
         <v>200</v>
       </c>
       <c r="E267" s="3" t="n">
-        <v>0.0384122919334187</v>
+        <v>0.03841229193341869</v>
       </c>
       <c r="F267" s="4" t="n">
         <v>30</v>
       </c>
       <c r="G267" s="3" t="n">
-        <v>0.653008962868118</v>
+        <v>0.6530089628681178</v>
       </c>
       <c r="H267" s="4" t="n">
         <v>510</v>
@@ -12522,7 +12522,7 @@
         </is>
       </c>
       <c r="C268" s="3" t="n">
-        <v>0.39622641509434</v>
+        <v>0.3962264150943396</v>
       </c>
       <c r="D268" s="4" t="n">
         <v>210</v>
@@ -12534,13 +12534,13 @@
         <v>0</v>
       </c>
       <c r="G268" s="3" t="n">
-        <v>0.541509433962264</v>
+        <v>0.5415094339622641</v>
       </c>
       <c r="H268" s="4" t="n">
         <v>287</v>
       </c>
       <c r="I268" s="3" t="n">
-        <v>0.00754716981132076</v>
+        <v>0.007547169811320755</v>
       </c>
       <c r="J268" s="4" t="n">
         <v>4</v>
@@ -12567,19 +12567,19 @@
         </is>
       </c>
       <c r="C269" s="3" t="n">
-        <v>0.285507246376812</v>
+        <v>0.2855072463768116</v>
       </c>
       <c r="D269" s="4" t="n">
         <v>197</v>
       </c>
       <c r="E269" s="3" t="n">
-        <v>0.0188405797101449</v>
+        <v>0.01884057971014493</v>
       </c>
       <c r="F269" s="4" t="n">
         <v>13</v>
       </c>
       <c r="G269" s="3" t="n">
-        <v>0.669565217391304</v>
+        <v>0.6695652173913044</v>
       </c>
       <c r="H269" s="4" t="n">
         <v>462</v>
@@ -12618,7 +12618,7 @@
         <v>0</v>
       </c>
       <c r="E270" s="3" t="n">
-        <v>0.9203296703296699</v>
+        <v>0.9203296703296703</v>
       </c>
       <c r="F270" s="4" t="n">
         <v>670</v>
@@ -12630,7 +12630,7 @@
         <v>34</v>
       </c>
       <c r="I270" s="3" t="n">
-        <v>0.00549450549450549</v>
+        <v>0.005494505494505495</v>
       </c>
       <c r="J270" s="4" t="n">
         <v>4</v>
@@ -12657,25 +12657,25 @@
         </is>
       </c>
       <c r="C271" s="3" t="n">
-        <v>0.0640465793304221</v>
+        <v>0.06404657933042213</v>
       </c>
       <c r="D271" s="4" t="n">
         <v>44</v>
       </c>
       <c r="E271" s="3" t="n">
-        <v>0.544395924308588</v>
+        <v>0.5443959243085881</v>
       </c>
       <c r="F271" s="4" t="n">
         <v>374</v>
       </c>
       <c r="G271" s="3" t="n">
-        <v>0.352256186317322</v>
+        <v>0.3522561863173217</v>
       </c>
       <c r="H271" s="4" t="n">
         <v>242</v>
       </c>
       <c r="I271" s="3" t="n">
-        <v>0.00582241630276565</v>
+        <v>0.005822416302765648</v>
       </c>
       <c r="J271" s="4" t="n">
         <v>4</v>
@@ -12708,19 +12708,19 @@
         <v>0</v>
       </c>
       <c r="E272" s="3" t="n">
-        <v>0.9341085271317831</v>
+        <v>0.9341085271317829</v>
       </c>
       <c r="F272" s="4" t="n">
         <v>723</v>
       </c>
       <c r="G272" s="3" t="n">
-        <v>0.0245478036175711</v>
+        <v>0.02454780361757106</v>
       </c>
       <c r="H272" s="4" t="n">
         <v>19</v>
       </c>
       <c r="I272" s="3" t="n">
-        <v>0.00129198966408269</v>
+        <v>0.001291989664082687</v>
       </c>
       <c r="J272" s="4" t="n">
         <v>1</v>
@@ -12747,25 +12747,25 @@
         </is>
       </c>
       <c r="C273" s="3" t="n">
-        <v>0.00815217391304348</v>
+        <v>0.008152173913043478</v>
       </c>
       <c r="D273" s="4" t="n">
         <v>3</v>
       </c>
       <c r="E273" s="3" t="n">
-        <v>0.809782608695652</v>
+        <v>0.8097826086956522</v>
       </c>
       <c r="F273" s="4" t="n">
         <v>298</v>
       </c>
       <c r="G273" s="3" t="n">
-        <v>0.14945652173913</v>
+        <v>0.1494565217391304</v>
       </c>
       <c r="H273" s="4" t="n">
         <v>55</v>
       </c>
       <c r="I273" s="3" t="n">
-        <v>0.00271739130434783</v>
+        <v>0.002717391304347826</v>
       </c>
       <c r="J273" s="4" t="n">
         <v>1</v>
@@ -12792,25 +12792,25 @@
         </is>
       </c>
       <c r="C274" s="3" t="n">
-        <v>0.031636863823934</v>
+        <v>0.03163686382393398</v>
       </c>
       <c r="D274" s="4" t="n">
         <v>23</v>
       </c>
       <c r="E274" s="3" t="n">
-        <v>0.768913342503439</v>
+        <v>0.7689133425034388</v>
       </c>
       <c r="F274" s="4" t="n">
         <v>559</v>
       </c>
       <c r="G274" s="3" t="n">
-        <v>0.178817056396149</v>
+        <v>0.1788170563961486</v>
       </c>
       <c r="H274" s="4" t="n">
         <v>130</v>
       </c>
       <c r="I274" s="3" t="n">
-        <v>0.00412654745529574</v>
+        <v>0.004126547455295736</v>
       </c>
       <c r="J274" s="4" t="n">
         <v>3</v>
@@ -12843,19 +12843,19 @@
         <v>2</v>
       </c>
       <c r="E275" s="3" t="n">
-        <v>0.849489795918367</v>
+        <v>0.8494897959183674</v>
       </c>
       <c r="F275" s="4" t="n">
         <v>333</v>
       </c>
       <c r="G275" s="3" t="n">
-        <v>0.102040816326531</v>
+        <v>0.1020408163265306</v>
       </c>
       <c r="H275" s="4" t="n">
         <v>40</v>
       </c>
       <c r="I275" s="3" t="n">
-        <v>0.00255102040816327</v>
+        <v>0.002551020408163265</v>
       </c>
       <c r="J275" s="4" t="n">
         <v>1</v>
@@ -12882,19 +12882,19 @@
         </is>
       </c>
       <c r="C276" s="3" t="n">
-        <v>0.00849256900212314</v>
+        <v>0.008492569002123142</v>
       </c>
       <c r="D276" s="4" t="n">
         <v>8</v>
       </c>
       <c r="E276" s="3" t="n">
-        <v>0.8057324840764331</v>
+        <v>0.8057324840764332</v>
       </c>
       <c r="F276" s="4" t="n">
         <v>759</v>
       </c>
       <c r="G276" s="3" t="n">
-        <v>0.146496815286624</v>
+        <v>0.1464968152866242</v>
       </c>
       <c r="H276" s="4" t="n">
         <v>138</v>
@@ -12927,25 +12927,25 @@
         </is>
       </c>
       <c r="C277" s="3" t="n">
-        <v>0.221864951768489</v>
+        <v>0.2218649517684887</v>
       </c>
       <c r="D277" s="4" t="n">
         <v>138</v>
       </c>
       <c r="E277" s="3" t="n">
-        <v>0.226688102893891</v>
+        <v>0.2266881028938907</v>
       </c>
       <c r="F277" s="4" t="n">
         <v>141</v>
       </c>
       <c r="G277" s="3" t="n">
-        <v>0.482315112540193</v>
+        <v>0.4823151125401929</v>
       </c>
       <c r="H277" s="4" t="n">
         <v>300</v>
       </c>
       <c r="I277" s="3" t="n">
-        <v>0.0321543408360129</v>
+        <v>0.03215434083601286</v>
       </c>
       <c r="J277" s="4" t="n">
         <v>20</v>
@@ -12972,13 +12972,13 @@
         </is>
       </c>
       <c r="C278" s="3" t="n">
-        <v>0.29940119760479</v>
+        <v>0.2994011976047904</v>
       </c>
       <c r="D278" s="4" t="n">
         <v>250</v>
       </c>
       <c r="E278" s="3" t="n">
-        <v>0.00598802395209581</v>
+        <v>0.005988023952095809</v>
       </c>
       <c r="F278" s="4" t="n">
         <v>5</v>
@@ -12990,7 +12990,7 @@
         <v>514</v>
       </c>
       <c r="I278" s="3" t="n">
-        <v>0.0347305389221557</v>
+        <v>0.03473053892215569</v>
       </c>
       <c r="J278" s="4" t="n">
         <v>29</v>
@@ -13017,25 +13017,25 @@
         </is>
       </c>
       <c r="C279" s="3" t="n">
-        <v>0.209889001009082</v>
+        <v>0.2098890010090817</v>
       </c>
       <c r="D279" s="4" t="n">
         <v>208</v>
       </c>
       <c r="E279" s="3" t="n">
-        <v>0.302724520686176</v>
+        <v>0.3027245206861756</v>
       </c>
       <c r="F279" s="4" t="n">
         <v>300</v>
       </c>
       <c r="G279" s="3" t="n">
-        <v>0.446014127144299</v>
+        <v>0.4460141271442987</v>
       </c>
       <c r="H279" s="4" t="n">
         <v>442</v>
       </c>
       <c r="I279" s="3" t="n">
-        <v>0.0100908173562059</v>
+        <v>0.01009081735620585</v>
       </c>
       <c r="J279" s="4" t="n">
         <v>10</v>
@@ -13062,19 +13062,19 @@
         </is>
       </c>
       <c r="C280" s="3" t="n">
-        <v>0.0063391442155309</v>
+        <v>0.006339144215530904</v>
       </c>
       <c r="D280" s="4" t="n">
         <v>4</v>
       </c>
       <c r="E280" s="3" t="n">
-        <v>0.789223454833597</v>
+        <v>0.7892234548335975</v>
       </c>
       <c r="F280" s="4" t="n">
         <v>498</v>
       </c>
       <c r="G280" s="3" t="n">
-        <v>0.175911251980983</v>
+        <v>0.1759112519809826</v>
       </c>
       <c r="H280" s="4" t="n">
         <v>111</v>
@@ -13113,19 +13113,19 @@
         <v>0</v>
       </c>
       <c r="E281" s="3" t="n">
-        <v>0.773451327433628</v>
+        <v>0.7734513274336283</v>
       </c>
       <c r="F281" s="4" t="n">
         <v>437</v>
       </c>
       <c r="G281" s="3" t="n">
-        <v>0.191150442477876</v>
+        <v>0.1911504424778761</v>
       </c>
       <c r="H281" s="4" t="n">
         <v>108</v>
       </c>
       <c r="I281" s="3" t="n">
-        <v>0.00176991150442478</v>
+        <v>0.001769911504424779</v>
       </c>
       <c r="J281" s="4" t="n">
         <v>1</v>
@@ -13152,25 +13152,25 @@
         </is>
       </c>
       <c r="C282" s="3" t="n">
-        <v>0.0120967741935484</v>
+        <v>0.01209677419354839</v>
       </c>
       <c r="D282" s="4" t="n">
         <v>9</v>
       </c>
       <c r="E282" s="3" t="n">
-        <v>0.845430107526882</v>
+        <v>0.8454301075268817</v>
       </c>
       <c r="F282" s="4" t="n">
         <v>629</v>
       </c>
       <c r="G282" s="3" t="n">
-        <v>0.118279569892473</v>
+        <v>0.1182795698924731</v>
       </c>
       <c r="H282" s="4" t="n">
         <v>88</v>
       </c>
       <c r="I282" s="3" t="n">
-        <v>0.010752688172043</v>
+        <v>0.01075268817204301</v>
       </c>
       <c r="J282" s="4" t="n">
         <v>8</v>
@@ -13197,25 +13197,25 @@
         </is>
       </c>
       <c r="C283" s="3" t="n">
-        <v>0.0229132569558101</v>
+        <v>0.02291325695581015</v>
       </c>
       <c r="D283" s="4" t="n">
         <v>14</v>
       </c>
       <c r="E283" s="3" t="n">
-        <v>0.775777414075286</v>
+        <v>0.7757774140752864</v>
       </c>
       <c r="F283" s="4" t="n">
         <v>474</v>
       </c>
       <c r="G283" s="3" t="n">
-        <v>0.165302782324059</v>
+        <v>0.1653027823240589</v>
       </c>
       <c r="H283" s="4" t="n">
         <v>101</v>
       </c>
       <c r="I283" s="3" t="n">
-        <v>0.00818330605564648</v>
+        <v>0.008183306055646482</v>
       </c>
       <c r="J283" s="4" t="n">
         <v>5</v>
@@ -13242,19 +13242,19 @@
         </is>
       </c>
       <c r="C284" s="3" t="n">
-        <v>0.0187265917602996</v>
+        <v>0.01872659176029963</v>
       </c>
       <c r="D284" s="4" t="n">
         <v>15</v>
       </c>
       <c r="E284" s="3" t="n">
-        <v>0.0100499375780275</v>
+        <v>0.01004993757802747</v>
       </c>
       <c r="F284" s="4" t="n">
         <v>8</v>
       </c>
       <c r="G284" s="3" t="n">
-        <v>0.199750312109863</v>
+        <v>0.1997503121098627</v>
       </c>
       <c r="H284" s="4" t="n">
         <v>160</v>
@@ -13299,7 +13299,7 @@
         <v>630</v>
       </c>
       <c r="G285" s="3" t="n">
-        <v>0.136125654450262</v>
+        <v>0.1361256544502618</v>
       </c>
       <c r="H285" s="4" t="n">
         <v>104</v>
@@ -13332,13 +13332,13 @@
         </is>
       </c>
       <c r="C286" s="3" t="n">
-        <v>0.171597633136095</v>
+        <v>0.1715976331360947</v>
       </c>
       <c r="D286" s="4" t="n">
         <v>174</v>
       </c>
       <c r="E286" s="3" t="n">
-        <v>0.275147928994083</v>
+        <v>0.2751479289940829</v>
       </c>
       <c r="F286" s="4" t="n">
         <v>279</v>
@@ -13350,7 +13350,7 @@
         <v>522</v>
       </c>
       <c r="I286" s="3" t="n">
-        <v>0.00493096646942801</v>
+        <v>0.004930966469428008</v>
       </c>
       <c r="J286" s="4" t="n">
         <v>5</v>
@@ -13377,19 +13377,19 @@
         <v>38220</v>
       </c>
       <c r="E287" s="3" t="n">
-        <v>0.31646661846228</v>
+        <v>0.3164666184622801</v>
       </c>
       <c r="F287" s="4" t="n">
         <v>65651</v>
       </c>
       <c r="G287" s="3" t="n">
-        <v>0.463875632682574</v>
+        <v>0.4638756326825741</v>
       </c>
       <c r="H287" s="4" t="n">
         <v>96231</v>
       </c>
       <c r="I287" s="3" t="n">
-        <v>0.00961677512653652</v>
+        <v>0.009616775126536515</v>
       </c>
       <c r="J287" s="4" t="n">
         <v>1995</v>
@@ -13406,25 +13406,25 @@
       <c r="A288" s="2" t="n"/>
       <c r="B288" s="2" t="n"/>
       <c r="C288" s="3" t="n">
-        <v>0.123576309794989</v>
+        <v>0.1235763097949886</v>
       </c>
       <c r="D288" s="4" t="n">
         <v>217</v>
       </c>
       <c r="E288" s="3" t="n">
-        <v>0.372437357630979</v>
+        <v>0.3724373576309795</v>
       </c>
       <c r="F288" s="4" t="n">
         <v>654</v>
       </c>
       <c r="G288" s="3" t="n">
-        <v>0.486332574031891</v>
+        <v>0.4863325740318907</v>
       </c>
       <c r="H288" s="4" t="n">
         <v>854</v>
       </c>
       <c r="I288" s="3" t="n">
-        <v>0.0113895216400911</v>
+        <v>0.01138952164009112</v>
       </c>
       <c r="J288" s="4" t="n">
         <v>20</v>
@@ -13441,25 +13441,25 @@
       <c r="A289" s="2" t="n"/>
       <c r="B289" s="2" t="n"/>
       <c r="C289" s="3" t="n">
-        <v>0.183722731009694</v>
+        <v>0.1837227310096935</v>
       </c>
       <c r="D289" s="4" t="n">
         <v>38437</v>
       </c>
       <c r="E289" s="3" t="n">
-        <v>0.316927327304361</v>
+        <v>0.3169273273043611</v>
       </c>
       <c r="F289" s="4" t="n">
         <v>66305</v>
       </c>
       <c r="G289" s="3" t="n">
-        <v>0.464050819264669</v>
+        <v>0.4640508192646693</v>
       </c>
       <c r="H289" s="4" t="n">
         <v>97085</v>
       </c>
       <c r="I289" s="3" t="n">
-        <v>0.00963137869720666</v>
+        <v>0.009631378697206662</v>
       </c>
       <c r="J289" s="4" t="n">
         <v>2015</v>
